--- a/patient_control_sheet.xlsx
+++ b/patient_control_sheet.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30006"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="1840" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCFC14B6-2BBA-42C5-ABE6-BA9677655276}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ksargur/Documents/UPenn/Lab Docs/Projects/Patient Control/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E88154FA-48E2-C04E-901F-7A6BD64B043C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" firstSheet="2" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Control" sheetId="1" r:id="rId1"/>
@@ -67,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1287" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1406" uniqueCount="447">
   <si>
     <t>Case</t>
   </si>
@@ -1237,6 +1242,177 @@
   </si>
   <si>
     <t>EMG x7 (brachioradialis, posterior/anterior compartment, biceps, triceps, lateral delts, anterior delts)</t>
+  </si>
+  <si>
+    <t>Bad Event Index</t>
+  </si>
+  <si>
+    <t>Median Nerve Stimulation</t>
+  </si>
+  <si>
+    <t>001_Thalamus15_260417_mediannerve.h5</t>
+  </si>
+  <si>
+    <t>MER Recording 1</t>
+  </si>
+  <si>
+    <t>002_Thalamus15_260417_MER1.h5</t>
+  </si>
+  <si>
+    <t>MER Recording 2</t>
+  </si>
+  <si>
+    <t>003_Thalamus15_260417_MER2.h5</t>
+  </si>
+  <si>
+    <t>004_Thalamus15_260417_baseline_eyeclose.h5</t>
+  </si>
+  <si>
+    <t>005_Thalamus15_260417_baseline_eyeopen.h5</t>
+  </si>
+  <si>
+    <t>Digit Flex/Ext</t>
+  </si>
+  <si>
+    <t>006_Thalamus15_260417_digit_flex_ext_edited.h5</t>
+  </si>
+  <si>
+    <t>Digit Block Rapid</t>
+  </si>
+  <si>
+    <t>007_Thalamus15_260417_digit_blockrapid_edited.h5</t>
+  </si>
+  <si>
+    <t>008_Thalamus15_260417_gesture1_edited.h5</t>
+  </si>
+  <si>
+    <t>Breakdance 1</t>
+  </si>
+  <si>
+    <t>009_Thalamus15_260417_breakdance1_edited.h5</t>
+  </si>
+  <si>
+    <t>010_Thalamus15_260417_gesture2_edited.h5</t>
+  </si>
+  <si>
+    <t>Paddle Hold 1</t>
+  </si>
+  <si>
+    <t>011_Thalamus15_260417_paddle_hold1.h5</t>
+  </si>
+  <si>
+    <t>Paddle Hold 2</t>
+  </si>
+  <si>
+    <t>012_Thalamus15_260417_paddle_hold2.h5</t>
+  </si>
+  <si>
+    <t>Paddle Hold 3</t>
+  </si>
+  <si>
+    <t>013_Thalamus15_260417_paddle_hold3.h5</t>
+  </si>
+  <si>
+    <t>Open/Close Slow</t>
+  </si>
+  <si>
+    <t>014_Thalamus15_260417_openclose_slow.h5</t>
+  </si>
+  <si>
+    <t>Breakdance 2</t>
+  </si>
+  <si>
+    <t>015_Thalamus15_260417_breakdance2.h5</t>
+  </si>
+  <si>
+    <t>016_Thalamus15_260417_DBS.h5</t>
+  </si>
+  <si>
+    <t>Missing trial 1</t>
+  </si>
+  <si>
+    <t>2:20pm (75 trials, 5 flexion/extensions per cue in radis succession)</t>
+  </si>
+  <si>
+    <t>Held arm with elbow against chest</t>
+  </si>
+  <si>
+    <t>Held arm outstretched</t>
+  </si>
+  <si>
+    <t>Held outstretched and opened and closed hand slowly</t>
+  </si>
+  <si>
+    <t>Held arm with shoulder outstreched, elbow bent and hand towards face --&gt; most tremor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DBS data corrupted </t>
+  </si>
+  <si>
+    <t>Very visible movement and artifact seen on EMG for syncronization</t>
+  </si>
+  <si>
+    <t>Thumb Stimulation 1</t>
+  </si>
+  <si>
+    <t>001_Thalamus14_thumb_stim_1.h5</t>
+  </si>
+  <si>
+    <t>Thumb Stimulation 2</t>
+  </si>
+  <si>
+    <t>002_Thalamus14_thumb_stim_2.h5</t>
+  </si>
+  <si>
+    <t>Index Stimulation (fail)</t>
+  </si>
+  <si>
+    <t>003_Thalamus14_index_stim_fail.h5</t>
+  </si>
+  <si>
+    <t>004_Thalamus14_index_stim.h5</t>
+  </si>
+  <si>
+    <t>005_Thalamus14_baseline_eyes_closed.h5</t>
+  </si>
+  <si>
+    <t>006_Thalamus14_baseline_eyes_open.h5</t>
+  </si>
+  <si>
+    <t>Digit 1</t>
+  </si>
+  <si>
+    <t>007_Thalamus14_digit_1.h5</t>
+  </si>
+  <si>
+    <t>008_Thalamus14_gesture_1.h5</t>
+  </si>
+  <si>
+    <t>Digit 2</t>
+  </si>
+  <si>
+    <t>009_Thalamus14_digit_2.h5</t>
+  </si>
+  <si>
+    <t>010_Thalamus14_gesture_2.h5</t>
+  </si>
+  <si>
+    <t>Gesture 3</t>
+  </si>
+  <si>
+    <t>011_Thalamus14_gesture_3.h5</t>
+  </si>
+  <si>
+    <t>012_Thalamus14_dbs.h5</t>
+  </si>
+  <si>
+    <t>2:43pm (XX trials, randomized, ✊👌🤙, baseline ✋</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Movement was difficult for patient, multiple fingers moved </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lost random singal, Movement was difficult for patient, multiple fingers moved </t>
   </si>
 </sst>
 </file>
@@ -1246,7 +1422,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="00000"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1301,6 +1477,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1421,13 +1603,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1435,12 +1616,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1456,20 +1631,19 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
@@ -1478,7 +1652,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1495,7 +1668,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1515,14 +1688,14 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="135">
+  <dxfs count="89">
     <dxf>
       <font>
-        <color theme="0" tint="-4.9989318521683403E-2"/>
+        <color rgb="FF006100"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1538,11 +1711,111 @@
     </dxf>
     <dxf>
       <font>
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1588,11 +1861,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <color theme="0" tint="-4.9989318521683403E-2"/>
       </font>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+        <patternFill patternType="solid">
+          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1603,6 +1876,16 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1638,21 +1921,21 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1688,21 +1971,21 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1738,21 +2021,21 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1783,86 +2066,6 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1918,71 +2121,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color theme="0" tint="-4.9989318521683403E-2"/>
       </font>
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2038,11 +2181,21 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2058,31 +2211,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <color theme="0" tint="-4.9989318521683403E-2"/>
       </font>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+        <patternFill patternType="solid">
+          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2158,41 +2291,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2258,181 +2361,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2558,16 +2491,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -2656,216 +2579,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <colors>
@@ -2892,9 +2605,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2932,7 +2645,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -3038,7 +2751,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3180,7 +2893,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3197,772 +2910,772 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N19"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="11" customWidth="1"/>
     <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.5703125" customWidth="1"/>
-    <col min="8" max="8" width="4.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="13.7109375" customWidth="1"/>
-    <col min="14" max="14" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="13.6640625" customWidth="1"/>
+    <col min="14" max="14" width="9.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="17" customFormat="1">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="1:14" s="14" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="F1" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="24" t="s">
+      <c r="G1" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="24" t="s">
+      <c r="H1" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="24" t="s">
+      <c r="I1" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="25" t="s">
+      <c r="J1" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="24" t="s">
+      <c r="K1" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="24" t="s">
+      <c r="L1" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="24" t="s">
+      <c r="M1" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="24" t="s">
+      <c r="N1" s="21" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="20" customFormat="1">
-      <c r="A2" s="26" t="s">
+    <row r="2" spans="1:14" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="28">
+      <c r="D2" s="24">
         <v>45303</v>
       </c>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27" t="s">
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27"/>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="23" t="s">
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A3" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="C3" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="31">
+      <c r="D3" s="27">
         <v>45324</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="E3" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="23"/>
-      <c r="G3" s="27" t="s">
+      <c r="F3" s="20"/>
+      <c r="G3" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="23" t="s">
+      <c r="H3" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="23" t="s">
+      <c r="I3" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="32" t="s">
+      <c r="J3" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="K3" s="32" t="s">
+      <c r="K3" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="L3" s="32" t="s">
+      <c r="L3" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="M3" s="32" t="s">
+      <c r="M3" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="N3" s="32" t="s">
+      <c r="N3" s="28" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="23" t="s">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A4" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="23" t="s">
+      <c r="B4" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="C4" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="31">
+      <c r="D4" s="27">
         <v>45345</v>
       </c>
-      <c r="E4" s="23" t="s">
+      <c r="E4" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="23"/>
-      <c r="G4" s="27" t="s">
+      <c r="F4" s="20"/>
+      <c r="G4" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="23" t="s">
+      <c r="H4" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="I4" s="23" t="s">
+      <c r="I4" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="32" t="s">
+      <c r="J4" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="K4" s="32" t="s">
+      <c r="K4" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="L4" s="32" t="s">
+      <c r="L4" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="M4" s="32" t="s">
+      <c r="M4" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="N4" s="32" t="s">
+      <c r="N4" s="28" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="23" t="s">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A5" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="33" t="s">
+      <c r="C5" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="31">
+      <c r="D5" s="27">
         <v>45380</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="E5" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="23"/>
-      <c r="G5" s="27" t="s">
+      <c r="F5" s="20"/>
+      <c r="G5" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="H5" s="23" t="s">
+      <c r="H5" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="I5" s="23" t="s">
+      <c r="I5" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="J5" s="32" t="s">
+      <c r="J5" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="K5" s="32" t="s">
+      <c r="K5" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="L5" s="32" t="s">
+      <c r="L5" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="M5" s="32" t="s">
+      <c r="M5" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="N5" s="32" t="s">
+      <c r="N5" s="28" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="23" t="s">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A6" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="33" t="s">
+      <c r="C6" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="27">
         <v>45450</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="22"/>
-      <c r="G6" s="27" t="s">
+      <c r="F6" s="19"/>
+      <c r="G6" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="34" t="s">
+      <c r="H6" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="I6" s="23" t="s">
+      <c r="I6" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="J6" s="32" t="s">
+      <c r="J6" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="K6" s="32" t="s">
+      <c r="K6" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="L6" s="32" t="s">
+      <c r="L6" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="M6" s="32" t="s">
+      <c r="M6" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="N6" s="32" t="s">
+      <c r="N6" s="28" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="23" t="s">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A7" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="33" t="s">
+      <c r="C7" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="27">
         <v>45457</v>
       </c>
-      <c r="E7" s="23" t="s">
+      <c r="E7" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="23"/>
-      <c r="G7" s="27" t="s">
+      <c r="F7" s="20"/>
+      <c r="G7" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="H7" s="23" t="s">
+      <c r="H7" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="I7" s="23" t="s">
+      <c r="I7" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="J7" s="32" t="s">
+      <c r="J7" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="K7" s="32" t="s">
+      <c r="K7" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="L7" s="32" t="s">
+      <c r="L7" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="M7" s="32" t="s">
+      <c r="M7" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="N7" s="32" t="s">
+      <c r="N7" s="28" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="23" t="s">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A8" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="33" t="s">
+      <c r="C8" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="27">
         <v>45520</v>
       </c>
-      <c r="E8" s="23" t="s">
+      <c r="E8" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="23"/>
-      <c r="G8" s="27" t="s">
+      <c r="F8" s="20"/>
+      <c r="G8" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="23" t="s">
+      <c r="H8" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="I8" s="23" t="s">
+      <c r="I8" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="J8" s="32" t="s">
+      <c r="J8" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="K8" s="32" t="s">
+      <c r="K8" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="L8" s="32" t="s">
+      <c r="L8" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="M8" s="32" t="s">
+      <c r="M8" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="N8" s="32" t="s">
+      <c r="N8" s="28" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="23" t="s">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A9" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="33" t="s">
+      <c r="C9" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="27">
         <v>45541</v>
       </c>
-      <c r="E9" s="23" t="s">
+      <c r="E9" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="F9" s="23"/>
-      <c r="G9" s="27" t="s">
+      <c r="F9" s="20"/>
+      <c r="G9" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="H9" s="23" t="s">
+      <c r="H9" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="I9" s="23" t="s">
+      <c r="I9" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="J9" s="32" t="s">
+      <c r="J9" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="K9" s="32" t="s">
+      <c r="K9" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="L9" s="32" t="s">
+      <c r="L9" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="M9" s="32" t="s">
+      <c r="M9" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="N9" s="32" t="s">
+      <c r="N9" s="28" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="23" t="s">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A10" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="33" t="s">
+      <c r="C10" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="27">
         <v>45548</v>
       </c>
-      <c r="E10" s="23" t="s">
+      <c r="E10" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="23"/>
-      <c r="G10" s="27" t="s">
+      <c r="F10" s="20"/>
+      <c r="G10" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="23" t="s">
+      <c r="H10" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="I10" s="23" t="s">
+      <c r="I10" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="J10" s="32" t="s">
+      <c r="J10" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="K10" s="32" t="s">
+      <c r="K10" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="L10" s="32" t="s">
+      <c r="L10" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="M10" s="32" t="s">
+      <c r="M10" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="N10" s="32" t="s">
+      <c r="N10" s="28" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="23" t="s">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A11" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="50" t="s">
+      <c r="C11" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="51"/>
-      <c r="E11" s="51"/>
-      <c r="F11" s="51"/>
-      <c r="G11" s="51"/>
-      <c r="H11" s="51"/>
-      <c r="I11" s="51"/>
-      <c r="J11" s="51"/>
-      <c r="K11" s="51"/>
-      <c r="L11" s="51"/>
-      <c r="M11" s="51"/>
-      <c r="N11" s="51"/>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="23" t="s">
+      <c r="D11" s="46"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="46"/>
+      <c r="G11" s="46"/>
+      <c r="H11" s="46"/>
+      <c r="I11" s="46"/>
+      <c r="J11" s="46"/>
+      <c r="K11" s="46"/>
+      <c r="L11" s="46"/>
+      <c r="M11" s="46"/>
+      <c r="N11" s="46"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A12" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="35" t="s">
+      <c r="C12" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="36">
+      <c r="D12" s="31">
         <v>45597</v>
       </c>
-      <c r="E12" s="35" t="s">
+      <c r="E12" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="F12" s="35"/>
-      <c r="G12" s="37" t="s">
+      <c r="F12" s="30"/>
+      <c r="G12" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="H12" s="35" t="s">
+      <c r="H12" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="I12" s="35" t="s">
+      <c r="I12" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="J12" s="38" t="s">
+      <c r="J12" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="K12" s="32" t="s">
+      <c r="K12" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="L12" s="32" t="s">
+      <c r="L12" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="M12" s="32" t="s">
+      <c r="M12" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="N12" s="32" t="s">
+      <c r="N12" s="28" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="42" t="s">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A13" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="B13" s="42" t="s">
+      <c r="B13" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="43" t="s">
+      <c r="C13" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="D13" s="44">
+      <c r="D13" s="39">
         <v>45597</v>
       </c>
-      <c r="E13" s="42" t="s">
+      <c r="E13" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="F13" s="42"/>
-      <c r="G13" s="45" t="s">
+      <c r="F13" s="37"/>
+      <c r="G13" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="H13" s="42" t="s">
+      <c r="H13" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="I13" s="42" t="s">
+      <c r="I13" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="J13" s="46" t="s">
+      <c r="J13" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="K13" s="46" t="s">
+      <c r="K13" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="L13" s="46" t="s">
+      <c r="L13" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="M13" s="47" t="s">
+      <c r="M13" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="N13" s="46" t="s">
+      <c r="N13" s="41" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="23" t="s">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A14" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="33" t="s">
+      <c r="C14" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="D14" s="31">
+      <c r="D14" s="27">
         <v>42097</v>
       </c>
-      <c r="E14" s="48" t="s">
+      <c r="E14" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="23"/>
-      <c r="G14" s="48" t="s">
+      <c r="F14" s="20"/>
+      <c r="G14" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="49" t="s">
+      <c r="H14" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="I14" s="23"/>
-      <c r="J14" s="46" t="s">
+      <c r="I14" s="20"/>
+      <c r="J14" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="K14" s="46" t="s">
+      <c r="K14" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="L14" s="46" t="s">
+      <c r="L14" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="M14" s="47" t="s">
+      <c r="M14" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="N14" s="46" t="s">
+      <c r="N14" s="41" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="23" t="s">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A15" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="33" t="s">
+      <c r="C15" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="31">
+      <c r="D15" s="27">
         <v>45793</v>
       </c>
-      <c r="E15" s="48" t="s">
+      <c r="E15" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="23"/>
-      <c r="G15" s="48" t="s">
+      <c r="F15" s="20"/>
+      <c r="G15" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="H15" s="49" t="s">
+      <c r="H15" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="I15" s="23"/>
-      <c r="J15" s="46" t="s">
+      <c r="I15" s="20"/>
+      <c r="J15" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="K15" s="46" t="s">
+      <c r="K15" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="L15" s="46" t="s">
+      <c r="L15" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="M15" s="47" t="s">
+      <c r="M15" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="N15" s="46" t="s">
+      <c r="N15" s="41" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
-      <c r="A16" s="23" t="s">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A16" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="33" t="s">
+      <c r="C16" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="31">
+      <c r="D16" s="27">
         <v>45807</v>
       </c>
-      <c r="E16" s="48" t="s">
+      <c r="E16" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="F16" s="23"/>
-      <c r="G16" s="48" t="s">
+      <c r="F16" s="20"/>
+      <c r="G16" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="H16" s="49" t="s">
+      <c r="H16" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="I16" s="23"/>
-      <c r="J16" s="46" t="s">
+      <c r="I16" s="20"/>
+      <c r="J16" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="K16" s="46" t="s">
+      <c r="K16" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="L16" s="46" t="s">
+      <c r="L16" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="M16" s="47" t="s">
+      <c r="M16" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="N16" s="46" t="s">
+      <c r="N16" s="41" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
-      <c r="A17" s="23" t="s">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A17" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="B17" s="23" t="s">
+      <c r="B17" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="33" t="s">
+      <c r="C17" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="D17" s="31">
+      <c r="D17" s="27">
         <v>46108</v>
       </c>
-      <c r="E17" s="23" t="s">
+      <c r="E17" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="F17" s="23"/>
-      <c r="G17" s="23" t="s">
+      <c r="F17" s="20"/>
+      <c r="G17" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H17" s="23" t="s">
+      <c r="H17" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="I17" s="23"/>
-      <c r="J17" s="46" t="s">
+      <c r="I17" s="20"/>
+      <c r="J17" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="K17" s="46" t="s">
+      <c r="K17" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="L17" s="46" t="s">
+      <c r="L17" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="M17" s="47" t="s">
+      <c r="M17" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="N17" s="46" t="s">
+      <c r="N17" s="41" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
-      <c r="A18" s="23" t="s">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A18" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="B18" s="23" t="s">
+      <c r="B18" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="33" t="s">
+      <c r="C18" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="D18" s="31">
+      <c r="D18" s="27">
         <v>46125</v>
       </c>
-      <c r="E18" s="23" t="s">
+      <c r="E18" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="F18" s="23"/>
-      <c r="G18" s="23" t="s">
+      <c r="F18" s="20"/>
+      <c r="G18" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H18" s="23" t="s">
+      <c r="H18" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="I18" s="23"/>
-      <c r="J18" s="38" t="s">
+      <c r="I18" s="20"/>
+      <c r="J18" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="K18" s="38" t="s">
+      <c r="K18" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="L18" s="38" t="s">
+      <c r="L18" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="M18" s="38" t="s">
+      <c r="M18" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="N18" s="38" t="s">
+      <c r="N18" s="33" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
-      <c r="A19" s="23" t="s">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A19" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="B19" s="23" t="s">
+      <c r="B19" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="33" t="s">
+      <c r="C19" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="D19" s="31">
+      <c r="D19" s="27">
         <v>46129</v>
       </c>
-      <c r="E19" s="23" t="s">
+      <c r="E19" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="F19" s="23"/>
-      <c r="G19" s="23" t="s">
+      <c r="F19" s="20"/>
+      <c r="G19" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="H19" s="23" t="s">
+      <c r="H19" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="I19" s="23" t="s">
+      <c r="I19" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="J19" s="38" t="s">
+      <c r="J19" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="K19" s="38" t="s">
+      <c r="K19" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="L19" s="38" t="s">
+      <c r="L19" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="M19" s="38" t="s">
+      <c r="M19" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="N19" s="38" t="s">
+      <c r="N19" s="33" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3970,134 +3683,20 @@
   <mergeCells count="1">
     <mergeCell ref="C11:N11"/>
   </mergeCells>
-  <conditionalFormatting sqref="J3:J10 J12:J18 K18:N18 J19:N19">
-    <cfRule type="containsText" dxfId="134" priority="42" operator="containsText" text="yes">
+  <conditionalFormatting sqref="J3:N10">
+    <cfRule type="notContainsText" dxfId="88" priority="3" operator="notContains" text="yes">
+      <formula>ISERROR(SEARCH("yes",J3))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="87" priority="4" operator="containsText" text="yes">
       <formula>NOT(ISERROR(SEARCH("yes",J3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J3:J10 J12:J18 K18:N18 J19:N19">
-    <cfRule type="notContainsText" dxfId="133" priority="41" operator="notContains" text="yes">
-      <formula>ISERROR(SEARCH("yes",J3))</formula>
+  <conditionalFormatting sqref="J12:N19">
+    <cfRule type="notContainsText" dxfId="86" priority="1" operator="notContains" text="yes">
+      <formula>ISERROR(SEARCH("yes",J12))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L3:M10 L12:M17">
-    <cfRule type="containsText" dxfId="132" priority="40" operator="containsText" text="yes">
-      <formula>NOT(ISERROR(SEARCH("yes",L3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L3:M10 L12:M17">
-    <cfRule type="notContainsText" dxfId="131" priority="39" operator="notContains" text="yes">
-      <formula>ISERROR(SEARCH("yes",L3))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K3:K10 K12:K17">
-    <cfRule type="containsText" dxfId="130" priority="38" operator="containsText" text="yes">
-      <formula>NOT(ISERROR(SEARCH("yes",K3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K3:K10 K12:K17">
-    <cfRule type="notContainsText" dxfId="129" priority="37" operator="notContains" text="yes">
-      <formula>ISERROR(SEARCH("yes",K3))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N12">
-    <cfRule type="containsText" dxfId="128" priority="28" operator="containsText" text="yes">
-      <formula>NOT(ISERROR(SEARCH("yes",N12)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N12">
-    <cfRule type="notContainsText" dxfId="127" priority="27" operator="notContains" text="yes">
-      <formula>ISERROR(SEARCH("yes",N12))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N3">
-    <cfRule type="containsText" dxfId="126" priority="18" operator="containsText" text="yes">
-      <formula>NOT(ISERROR(SEARCH("yes",N3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N3">
-    <cfRule type="notContainsText" dxfId="125" priority="17" operator="notContains" text="yes">
-      <formula>ISERROR(SEARCH("yes",N3))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N4">
-    <cfRule type="containsText" dxfId="124" priority="16" operator="containsText" text="yes">
-      <formula>NOT(ISERROR(SEARCH("yes",N4)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N4">
-    <cfRule type="notContainsText" dxfId="123" priority="15" operator="notContains" text="yes">
-      <formula>ISERROR(SEARCH("yes",N4))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N5">
-    <cfRule type="containsText" dxfId="122" priority="14" operator="containsText" text="yes">
-      <formula>NOT(ISERROR(SEARCH("yes",N5)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N5">
-    <cfRule type="notContainsText" dxfId="121" priority="13" operator="notContains" text="yes">
-      <formula>ISERROR(SEARCH("yes",N5))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N6">
-    <cfRule type="containsText" dxfId="120" priority="12" operator="containsText" text="yes">
-      <formula>NOT(ISERROR(SEARCH("yes",N6)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N6">
-    <cfRule type="notContainsText" dxfId="119" priority="11" operator="notContains" text="yes">
-      <formula>ISERROR(SEARCH("yes",N6))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N7">
-    <cfRule type="containsText" dxfId="118" priority="10" operator="containsText" text="yes">
-      <formula>NOT(ISERROR(SEARCH("yes",N7)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N7">
-    <cfRule type="notContainsText" dxfId="117" priority="9" operator="notContains" text="yes">
-      <formula>ISERROR(SEARCH("yes",N7))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N8">
-    <cfRule type="containsText" dxfId="116" priority="8" operator="containsText" text="yes">
-      <formula>NOT(ISERROR(SEARCH("yes",N8)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N8">
-    <cfRule type="notContainsText" dxfId="115" priority="7" operator="notContains" text="yes">
-      <formula>ISERROR(SEARCH("yes",N8))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N9">
-    <cfRule type="containsText" dxfId="114" priority="6" operator="containsText" text="yes">
-      <formula>NOT(ISERROR(SEARCH("yes",N9)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N9">
-    <cfRule type="notContainsText" dxfId="113" priority="5" operator="notContains" text="yes">
-      <formula>ISERROR(SEARCH("yes",N9))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N10">
-    <cfRule type="containsText" dxfId="112" priority="4" operator="containsText" text="yes">
-      <formula>NOT(ISERROR(SEARCH("yes",N10)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N10">
-    <cfRule type="notContainsText" dxfId="111" priority="3" operator="notContains" text="yes">
-      <formula>ISERROR(SEARCH("yes",N10))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N13:N17">
-    <cfRule type="containsText" dxfId="110" priority="2" operator="containsText" text="yes">
-      <formula>NOT(ISERROR(SEARCH("yes",N13)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N13:N17">
-    <cfRule type="notContainsText" dxfId="109" priority="1" operator="notContains" text="yes">
-      <formula>ISERROR(SEARCH("yes",N13))</formula>
+    <cfRule type="containsText" dxfId="85" priority="2" operator="containsText" text="yes">
+      <formula>NOT(ISERROR(SEARCH("yes",J12)))</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
@@ -4130,81 +3729,81 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A76D327-328A-48EF-B1BF-49D6B0752FF3}">
   <dimension ref="A1:M32"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="39.42578125" customWidth="1"/>
-    <col min="3" max="3" width="40.42578125" customWidth="1"/>
-    <col min="4" max="4" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.5" customWidth="1"/>
+    <col min="3" max="3" width="40.5" customWidth="1"/>
+    <col min="4" max="4" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="17" customFormat="1">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="G1" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="H1" s="17" t="s">
+      <c r="H1" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="I1" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="J1" s="18" t="s">
+      <c r="J1" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="K1" s="17" t="s">
+      <c r="K1" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="L1" s="17" t="s">
+      <c r="L1" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="M1" s="18" t="s">
+      <c r="M1" s="15" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" t="s">
         <v>200</v>
       </c>
       <c r="C2" t="s">
         <v>264</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="F2" s="10"/>
+      <c r="D2" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F2" s="1"/>
       <c r="G2" t="s">
         <v>80</v>
       </c>
@@ -4227,17 +3826,17 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>83</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" t="s">
         <v>109</v>
       </c>
       <c r="C3" t="s">
         <v>265</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="3">
         <v>1</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -4266,17 +3865,17 @@
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>84</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" t="s">
         <v>109</v>
       </c>
       <c r="C4" t="s">
         <v>266</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="3">
         <v>2</v>
       </c>
       <c r="E4" s="1" t="s">
@@ -4305,15 +3904,15 @@
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>85</v>
       </c>
-      <c r="B5" s="11"/>
+      <c r="B5" s="8"/>
       <c r="C5" t="s">
         <v>267</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="3">
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
@@ -4339,15 +3938,15 @@
         <v>220</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>89</v>
       </c>
-      <c r="B6" s="11"/>
+      <c r="B6" s="8"/>
       <c r="C6" t="s">
         <v>268</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="3">
         <v>3</v>
       </c>
       <c r="E6" s="1" t="s">
@@ -4360,7 +3959,7 @@
       <c r="J6" t="s">
         <v>203</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="K6" s="8" t="s">
         <v>226</v>
       </c>
       <c r="L6" t="s">
@@ -4370,15 +3969,15 @@
         <v>228</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>269</v>
       </c>
-      <c r="B7" s="11"/>
+      <c r="B7" s="8"/>
       <c r="C7" t="s">
         <v>270</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="3">
         <v>5</v>
       </c>
       <c r="E7" s="1" t="s">
@@ -4407,15 +4006,15 @@
         <v>234</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>271</v>
       </c>
-      <c r="B8" s="11"/>
+      <c r="B8" s="8"/>
       <c r="C8" t="s">
         <v>272</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="3">
         <v>6</v>
       </c>
       <c r="E8" s="1" t="s">
@@ -4444,15 +4043,15 @@
         <v>245</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>95</v>
       </c>
-      <c r="B9" s="11"/>
+      <c r="B9" s="8"/>
       <c r="C9" t="s">
         <v>273</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="3">
         <v>7</v>
       </c>
       <c r="E9" s="1" t="s">
@@ -4481,15 +4080,15 @@
         <v>239</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>147</v>
       </c>
-      <c r="B10" s="11"/>
+      <c r="B10" s="8"/>
       <c r="C10" t="s">
         <v>274</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="3">
         <v>10</v>
       </c>
       <c r="E10" s="1" t="s">
@@ -4518,15 +4117,15 @@
         <v>80</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>275</v>
       </c>
-      <c r="B11" s="11"/>
+      <c r="B11" s="8"/>
       <c r="C11" t="s">
         <v>276</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="3">
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
@@ -4555,17 +4154,17 @@
         <v>80</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>150</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" t="s">
         <v>277</v>
       </c>
       <c r="C12" t="s">
         <v>278</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="3">
         <v>9</v>
       </c>
       <c r="E12" s="1" t="s">
@@ -4588,17 +4187,17 @@
         <v>80</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>102</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" t="s">
         <v>103</v>
       </c>
       <c r="C13" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="4" t="s">
         <v>47</v>
       </c>
       <c r="E13" s="1" t="s">
@@ -4612,44 +4211,37 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:13">
-      <c r="B16" s="19"/>
-    </row>
-    <row r="32" ht="22.5" customHeight="1"/>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B16" s="16"/>
+    </row>
+    <row r="32" ht="22.5" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <conditionalFormatting sqref="E3:F13">
-    <cfRule type="containsText" dxfId="32" priority="9" operator="containsText" text="done">
-      <formula>NOT(ISERROR(SEARCH("done",E3)))</formula>
+  <conditionalFormatting sqref="A1:XFD6 A7:J8 L7:XFD8 F8:XFD8 A9 C9:XFD9 A10:XFD1048576">
+    <cfRule type="cellIs" dxfId="43" priority="1" operator="equal">
+      <formula>"N/A"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:B8">
+    <cfRule type="containsText" dxfId="42" priority="6" operator="containsText" text="none">
+      <formula>NOT(ISERROR(SEARCH("none",B2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B10:B13">
+    <cfRule type="containsText" dxfId="41" priority="4" operator="containsText" text="none">
+      <formula>NOT(ISERROR(SEARCH("none",B10)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D13">
+    <cfRule type="containsText" dxfId="40" priority="7" operator="containsText" text="pending">
+      <formula>NOT(ISERROR(SEARCH("pending",D13)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:F13">
-    <cfRule type="containsText" dxfId="31" priority="8" operator="containsText" text="pending">
+    <cfRule type="containsText" dxfId="39" priority="8" operator="containsText" text="pending">
       <formula>NOT(ISERROR(SEARCH("pending",E3)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D13">
-    <cfRule type="containsText" dxfId="30" priority="7" operator="containsText" text="pending">
-      <formula>NOT(ISERROR(SEARCH("pending",D13)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B10:B11 B2:B8">
-    <cfRule type="containsText" dxfId="29" priority="6" operator="containsText" text="none">
-      <formula>NOT(ISERROR(SEARCH("none",B2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B13">
-    <cfRule type="containsText" dxfId="28" priority="5" operator="containsText" text="none">
-      <formula>NOT(ISERROR(SEARCH("none",B13)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B12">
-    <cfRule type="containsText" dxfId="27" priority="4" operator="containsText" text="none">
-      <formula>NOT(ISERROR(SEARCH("none",B12)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A9 L7:XFD8 F8:XFD8 A1:XFD6 A7:J8 C9:XFD9 A10:XFD1048576">
-    <cfRule type="cellIs" dxfId="26" priority="1" operator="equal">
-      <formula>"N/A"</formula>
+    <cfRule type="containsText" dxfId="38" priority="9" operator="containsText" text="done">
+      <formula>NOT(ISERROR(SEARCH("done",E3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4659,295 +4251,291 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50E3C3DA-8365-4B66-9510-EF3386D12886}">
   <dimension ref="A1:M18"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="27.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="38.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.83203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="23" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="26.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="26.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.33203125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="20" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="21" customHeight="1">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="34" t="s">
         <v>279</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="G1" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="H1" s="17" t="s">
+      <c r="H1" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="I1" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="J1" s="18" t="s">
+      <c r="J1" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="K1" s="17" t="s">
+      <c r="K1" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="L1" s="17" t="s">
+      <c r="L1" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="M1" s="18" t="s">
+      <c r="M1" s="15" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
       <c r="D2" t="s">
         <v>280</v>
       </c>
-      <c r="E2" s="41" t="s">
+      <c r="E2" s="36" t="s">
         <v>281</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>84</v>
       </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
       <c r="D3" t="s">
         <v>282</v>
       </c>
-      <c r="E3" s="41" t="s">
+      <c r="E3" s="36" t="s">
         <v>283</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>284</v>
       </c>
-      <c r="C4" s="40"/>
+      <c r="C4" s="35"/>
       <c r="D4" t="s">
         <v>285</v>
       </c>
-      <c r="E4" s="41" t="s">
+      <c r="E4" s="36" t="s">
         <v>286</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="16.5">
+    <row r="5" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>287</v>
       </c>
-      <c r="B5" s="40" t="s">
+      <c r="B5" s="35" t="s">
         <v>288</v>
       </c>
-      <c r="C5" s="40"/>
+      <c r="C5" s="35"/>
       <c r="D5" t="s">
         <v>289</v>
       </c>
-      <c r="E5" s="41" t="s">
+      <c r="E5" s="36" t="s">
         <v>290</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="16.5">
+    <row r="6" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>291</v>
       </c>
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="35" t="s">
         <v>288</v>
       </c>
-      <c r="C6" s="40"/>
+      <c r="C6" s="35"/>
       <c r="D6" t="s">
         <v>292</v>
       </c>
-      <c r="E6" s="41" t="s">
+      <c r="E6" s="36" t="s">
         <v>293</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>294</v>
       </c>
-      <c r="B7" s="40"/>
-      <c r="C7" s="40"/>
+      <c r="B7" s="35"/>
+      <c r="C7" s="35"/>
       <c r="D7" t="s">
         <v>295</v>
       </c>
-      <c r="E7" s="41" t="s">
+      <c r="E7" s="36" t="s">
         <v>296</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>297</v>
       </c>
-      <c r="B8" s="40"/>
-      <c r="C8" s="40"/>
+      <c r="B8" s="35"/>
+      <c r="C8" s="35"/>
       <c r="D8" t="s">
         <v>298</v>
       </c>
-      <c r="E8" s="41" t="s">
+      <c r="E8" s="36" t="s">
         <v>299</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>300</v>
       </c>
-      <c r="B9" s="40"/>
-      <c r="C9" s="40"/>
+      <c r="B9" s="35"/>
+      <c r="C9" s="35"/>
       <c r="D9" t="s">
         <v>301</v>
       </c>
-      <c r="E9" s="41" t="s">
+      <c r="E9" s="36" t="s">
         <v>302</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>303</v>
       </c>
-      <c r="B10" s="40"/>
-      <c r="C10" s="40"/>
+      <c r="B10" s="35"/>
+      <c r="C10" s="35"/>
       <c r="D10" t="s">
         <v>304</v>
       </c>
-      <c r="E10" s="41" t="s">
+      <c r="E10" s="36" t="s">
         <v>305</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>306</v>
       </c>
-      <c r="B11" s="40"/>
-      <c r="C11" s="40"/>
+      <c r="B11" s="35"/>
+      <c r="C11" s="35"/>
       <c r="D11" t="s">
         <v>307</v>
       </c>
-      <c r="E11" s="41" t="s">
+      <c r="E11" s="36" t="s">
         <v>308</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
-      <c r="B12" s="40"/>
-      <c r="C12" s="40"/>
-      <c r="E12" s="41"/>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="B13" s="40"/>
-      <c r="C13" s="40"/>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="17" t="s">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B12" s="35"/>
+      <c r="C12" s="35"/>
+      <c r="E12" s="36"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B13" s="35"/>
+      <c r="C13" s="35"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A14" s="14" t="s">
         <v>309</v>
       </c>
-      <c r="B14" s="40"/>
-      <c r="C14" s="40"/>
-    </row>
-    <row r="15" spans="1:13">
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>310</v>
       </c>
-      <c r="B15" s="40"/>
-      <c r="C15" s="40"/>
-    </row>
-    <row r="16" spans="1:13">
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>311</v>
       </c>
-      <c r="B16" s="40"/>
-      <c r="C16" s="40"/>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>312</v>
       </c>
-      <c r="B17" s="40"/>
-      <c r="C17" s="40"/>
-    </row>
-    <row r="18" spans="1:3">
+      <c r="B17" s="35"/>
+      <c r="C17" s="35"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>313</v>
       </c>
-      <c r="B18" s="40"/>
-      <c r="C18" s="40"/>
+      <c r="B18" s="35"/>
+      <c r="C18" s="35"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:M1">
-    <cfRule type="cellIs" dxfId="25" priority="5" operator="equal">
+  <conditionalFormatting sqref="A14">
+    <cfRule type="cellIs" dxfId="37" priority="4" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A14">
-    <cfRule type="cellIs" dxfId="24" priority="4" operator="equal">
+  <conditionalFormatting sqref="A1:M1">
+    <cfRule type="cellIs" dxfId="36" priority="5" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F11">
-    <cfRule type="containsText" dxfId="23" priority="3" operator="containsText" text="done">
-      <formula>NOT(ISERROR(SEARCH("done",F2)))</formula>
+    <cfRule type="cellIs" dxfId="35" priority="1" operator="equal">
+      <formula>"N/A"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F11">
-    <cfRule type="containsText" dxfId="22" priority="2" operator="containsText" text="pending">
+    <cfRule type="containsText" dxfId="34" priority="2" operator="containsText" text="pending">
       <formula>NOT(ISERROR(SEARCH("pending",F2)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F11">
-    <cfRule type="cellIs" dxfId="21" priority="1" operator="equal">
-      <formula>"N/A"</formula>
+    <cfRule type="containsText" dxfId="33" priority="3" operator="containsText" text="done">
+      <formula>NOT(ISERROR(SEARCH("done",F2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4957,303 +4545,299 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF1014AD-5C95-4D51-A4D0-26A7C8B0E371}">
   <dimension ref="A1:M18"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="27.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="47.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="47.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.83203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="23" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="26.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="26.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.33203125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="20" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="22.5" customHeight="1">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="34" t="s">
         <v>279</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="G1" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="H1" s="17" t="s">
+      <c r="H1" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="I1" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="J1" s="18" t="s">
+      <c r="J1" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="K1" s="17" t="s">
+      <c r="K1" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="L1" s="17" t="s">
+      <c r="L1" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="M1" s="18" t="s">
+      <c r="M1" s="15" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
       <c r="D2" t="s">
         <v>314</v>
       </c>
-      <c r="E2" s="41" t="s">
+      <c r="E2" s="36" t="s">
         <v>281</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>84</v>
       </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
       <c r="D3" t="s">
         <v>315</v>
       </c>
-      <c r="E3" s="41" t="s">
+      <c r="E3" s="36" t="s">
         <v>283</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>284</v>
       </c>
-      <c r="C4" s="40"/>
+      <c r="C4" s="35"/>
       <c r="D4" t="s">
         <v>316</v>
       </c>
-      <c r="E4" s="41" t="s">
+      <c r="E4" s="36" t="s">
         <v>286</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="16.5">
+    <row r="5" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>287</v>
       </c>
-      <c r="B5" s="40" t="s">
+      <c r="B5" s="35" t="s">
         <v>288</v>
       </c>
-      <c r="C5" s="40"/>
+      <c r="C5" s="35"/>
       <c r="D5" t="s">
         <v>317</v>
       </c>
-      <c r="E5" s="41" t="s">
+      <c r="E5" s="36" t="s">
         <v>290</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="16.5">
+    <row r="6" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>291</v>
       </c>
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="35" t="s">
         <v>288</v>
       </c>
-      <c r="C6" s="40"/>
+      <c r="C6" s="35"/>
       <c r="D6" t="s">
         <v>318</v>
       </c>
-      <c r="E6" s="41" t="s">
+      <c r="E6" s="36" t="s">
         <v>293</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>294</v>
       </c>
-      <c r="B7" s="40"/>
-      <c r="C7" s="40"/>
+      <c r="B7" s="35"/>
+      <c r="C7" s="35"/>
       <c r="D7" t="s">
         <v>319</v>
       </c>
-      <c r="E7" s="41" t="s">
+      <c r="E7" s="36" t="s">
         <v>296</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>297</v>
       </c>
-      <c r="B8" s="40"/>
-      <c r="C8" s="40"/>
+      <c r="B8" s="35"/>
+      <c r="C8" s="35"/>
       <c r="D8" t="s">
         <v>320</v>
       </c>
-      <c r="E8" s="41" t="s">
+      <c r="E8" s="36" t="s">
         <v>299</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>300</v>
       </c>
-      <c r="B9" s="40"/>
-      <c r="C9" s="40"/>
+      <c r="B9" s="35"/>
+      <c r="C9" s="35"/>
       <c r="D9" t="s">
         <v>321</v>
       </c>
-      <c r="E9" s="41" t="s">
+      <c r="E9" s="36" t="s">
         <v>302</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>303</v>
       </c>
-      <c r="B10" s="40"/>
-      <c r="C10" s="40"/>
+      <c r="B10" s="35"/>
+      <c r="C10" s="35"/>
       <c r="D10" t="s">
         <v>322</v>
       </c>
-      <c r="E10" s="41" t="s">
+      <c r="E10" s="36" t="s">
         <v>305</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>306</v>
       </c>
-      <c r="B11" s="40"/>
-      <c r="C11" s="40"/>
+      <c r="B11" s="35"/>
+      <c r="C11" s="35"/>
       <c r="D11" t="s">
         <v>323</v>
       </c>
-      <c r="E11" s="41" t="s">
+      <c r="E11" s="36" t="s">
         <v>308</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>324</v>
       </c>
-      <c r="B12" s="40"/>
-      <c r="C12" s="40"/>
+      <c r="B12" s="35"/>
+      <c r="C12" s="35"/>
       <c r="D12" t="s">
         <v>325</v>
       </c>
-      <c r="E12" s="41" t="s">
+      <c r="E12" s="36" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
-      <c r="B13" s="40"/>
-      <c r="C13" s="40"/>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="17" t="s">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B13" s="35"/>
+      <c r="C13" s="35"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A14" s="14" t="s">
         <v>309</v>
       </c>
-      <c r="B14" s="40"/>
-      <c r="C14" s="40"/>
-    </row>
-    <row r="15" spans="1:13">
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>310</v>
       </c>
-      <c r="B15" s="40"/>
-      <c r="C15" s="40"/>
-    </row>
-    <row r="16" spans="1:13">
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>311</v>
       </c>
-      <c r="B16" s="40"/>
-      <c r="C16" s="40"/>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>312</v>
       </c>
-      <c r="B17" s="40"/>
-      <c r="C17" s="40"/>
-    </row>
-    <row r="18" spans="1:3">
+      <c r="B17" s="35"/>
+      <c r="C17" s="35"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>313</v>
       </c>
-      <c r="B18" s="40"/>
-      <c r="C18" s="40"/>
+      <c r="B18" s="35"/>
+      <c r="C18" s="35"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:M1">
-    <cfRule type="cellIs" dxfId="20" priority="5" operator="equal">
+  <conditionalFormatting sqref="A14">
+    <cfRule type="cellIs" dxfId="32" priority="4" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A14">
-    <cfRule type="cellIs" dxfId="19" priority="4" operator="equal">
+  <conditionalFormatting sqref="A1:M1">
+    <cfRule type="cellIs" dxfId="31" priority="5" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F11">
-    <cfRule type="containsText" dxfId="18" priority="3" operator="containsText" text="done">
-      <formula>NOT(ISERROR(SEARCH("done",F2)))</formula>
+    <cfRule type="cellIs" dxfId="30" priority="1" operator="equal">
+      <formula>"N/A"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F11">
-    <cfRule type="containsText" dxfId="17" priority="2" operator="containsText" text="pending">
+    <cfRule type="containsText" dxfId="29" priority="2" operator="containsText" text="pending">
       <formula>NOT(ISERROR(SEARCH("pending",F2)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F11">
-    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
-      <formula>"N/A"</formula>
+    <cfRule type="containsText" dxfId="28" priority="3" operator="containsText" text="done">
+      <formula>NOT(ISERROR(SEARCH("done",F2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5263,284 +4847,280 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86BC1306-E052-4ADF-B4FC-5612FD988DAA}">
   <dimension ref="A1:M18"/>
-  <sheetFormatPr defaultColWidth="25.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="25.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="27.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="53.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="53.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25.5" customHeight="1">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="34" t="s">
         <v>279</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="G1" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="H1" s="17" t="s">
+      <c r="H1" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="I1" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="J1" s="18" t="s">
+      <c r="J1" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="K1" s="17" t="s">
+      <c r="K1" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="L1" s="17" t="s">
+      <c r="L1" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="M1" s="18" t="s">
+      <c r="M1" s="15" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
       <c r="D2" t="s">
         <v>327</v>
       </c>
-      <c r="E2" s="41" t="s">
+      <c r="E2" s="36" t="s">
         <v>281</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>84</v>
       </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
       <c r="D3" t="s">
         <v>328</v>
       </c>
-      <c r="E3" s="41" t="s">
+      <c r="E3" s="36" t="s">
         <v>283</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="16.5">
+    <row r="4" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>287</v>
       </c>
-      <c r="B4" s="40" t="s">
+      <c r="B4" s="35" t="s">
         <v>288</v>
       </c>
-      <c r="C4" s="40"/>
+      <c r="C4" s="35"/>
       <c r="D4" t="s">
         <v>329</v>
       </c>
-      <c r="E4" s="41" t="s">
+      <c r="E4" s="36" t="s">
         <v>286</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="16.5">
+    <row r="5" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>291</v>
       </c>
-      <c r="B5" s="40" t="s">
+      <c r="B5" s="35" t="s">
         <v>288</v>
       </c>
-      <c r="C5" s="40"/>
+      <c r="C5" s="35"/>
       <c r="D5" t="s">
         <v>330</v>
       </c>
-      <c r="E5" s="41" t="s">
+      <c r="E5" s="36" t="s">
         <v>290</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>294</v>
       </c>
-      <c r="B6" s="40"/>
-      <c r="C6" s="40"/>
+      <c r="B6" s="35"/>
+      <c r="C6" s="35"/>
       <c r="D6" t="s">
         <v>331</v>
       </c>
-      <c r="E6" s="41" t="s">
+      <c r="E6" s="36" t="s">
         <v>293</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>297</v>
       </c>
-      <c r="B7" s="40"/>
-      <c r="C7" s="40"/>
+      <c r="B7" s="35"/>
+      <c r="C7" s="35"/>
       <c r="D7" t="s">
         <v>332</v>
       </c>
-      <c r="E7" s="41" t="s">
+      <c r="E7" s="36" t="s">
         <v>296</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>300</v>
       </c>
-      <c r="B8" s="40"/>
-      <c r="C8" s="40"/>
+      <c r="B8" s="35"/>
+      <c r="C8" s="35"/>
       <c r="D8" t="s">
         <v>333</v>
       </c>
-      <c r="E8" s="41" t="s">
+      <c r="E8" s="36" t="s">
         <v>299</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>303</v>
       </c>
-      <c r="B9" s="40"/>
-      <c r="C9" s="40"/>
+      <c r="B9" s="35"/>
+      <c r="C9" s="35"/>
       <c r="D9" t="s">
         <v>334</v>
       </c>
-      <c r="E9" s="41" t="s">
+      <c r="E9" s="36" t="s">
         <v>302</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>306</v>
       </c>
-      <c r="B10" s="40"/>
-      <c r="C10" s="40"/>
+      <c r="B10" s="35"/>
+      <c r="C10" s="35"/>
       <c r="D10" t="s">
         <v>335</v>
       </c>
-      <c r="E10" s="41" t="s">
+      <c r="E10" s="36" t="s">
         <v>305</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>324</v>
       </c>
-      <c r="B11" s="40"/>
-      <c r="C11" s="40"/>
+      <c r="B11" s="35"/>
+      <c r="C11" s="35"/>
       <c r="D11" t="s">
         <v>336</v>
       </c>
-      <c r="E11" s="41" t="s">
+      <c r="E11" s="36" t="s">
         <v>308</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
-      <c r="B12" s="40"/>
-      <c r="C12" s="40"/>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="B13" s="40"/>
-      <c r="C13" s="40"/>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="17" t="s">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B12" s="35"/>
+      <c r="C12" s="35"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B13" s="35"/>
+      <c r="C13" s="35"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A14" s="14" t="s">
         <v>309</v>
       </c>
-      <c r="B14" s="40"/>
-      <c r="C14" s="40"/>
-    </row>
-    <row r="15" spans="1:13">
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>310</v>
       </c>
-      <c r="B15" s="40"/>
-      <c r="C15" s="40"/>
-    </row>
-    <row r="16" spans="1:13">
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>311</v>
       </c>
-      <c r="B16" s="40"/>
-      <c r="C16" s="40"/>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>312</v>
       </c>
-      <c r="B17" s="40"/>
-      <c r="C17" s="40"/>
-    </row>
-    <row r="18" spans="1:3">
+      <c r="B17" s="35"/>
+      <c r="C17" s="35"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>313</v>
       </c>
-      <c r="B18" s="40"/>
-      <c r="C18" s="40"/>
+      <c r="B18" s="35"/>
+      <c r="C18" s="35"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:M1">
-    <cfRule type="cellIs" dxfId="15" priority="5" operator="equal">
+  <conditionalFormatting sqref="A14">
+    <cfRule type="cellIs" dxfId="27" priority="4" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A14">
-    <cfRule type="cellIs" dxfId="14" priority="4" operator="equal">
+  <conditionalFormatting sqref="A1:M1">
+    <cfRule type="cellIs" dxfId="26" priority="5" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F11">
-    <cfRule type="containsText" dxfId="13" priority="3" operator="containsText" text="done">
-      <formula>NOT(ISERROR(SEARCH("done",F2)))</formula>
+    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
+      <formula>"N/A"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F11">
-    <cfRule type="containsText" dxfId="12" priority="2" operator="containsText" text="pending">
+    <cfRule type="containsText" dxfId="24" priority="2" operator="containsText" text="pending">
       <formula>NOT(ISERROR(SEARCH("pending",F2)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F11">
-    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
-      <formula>"N/A"</formula>
+    <cfRule type="containsText" dxfId="23" priority="3" operator="containsText" text="done">
+      <formula>NOT(ISERROR(SEARCH("done",F2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5550,389 +5130,385 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{804C5360-C00D-47DA-9764-99B96657F270}">
   <dimension ref="A1:M23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21.5703125" customWidth="1"/>
-    <col min="2" max="2" width="42.85546875" style="40" customWidth="1"/>
-    <col min="3" max="3" width="32.5703125" style="40" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="53.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.5" customWidth="1"/>
+    <col min="2" max="2" width="42.83203125" style="35" customWidth="1"/>
+    <col min="3" max="3" width="32.5" style="35" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="53.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.83203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="23" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="26.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="26.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.33203125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="20" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="34" t="s">
         <v>279</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="G1" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="H1" s="17" t="s">
+      <c r="H1" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="I1" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="J1" s="18" t="s">
+      <c r="J1" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="K1" s="17" t="s">
+      <c r="K1" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="L1" s="17" t="s">
+      <c r="L1" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="M1" s="18" t="s">
+      <c r="M1" s="15" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="30.75">
+    <row r="2" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>337</v>
       </c>
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="35" t="s">
         <v>338</v>
       </c>
-      <c r="C2" s="40" t="s">
+      <c r="C2" s="35" t="s">
         <v>339</v>
       </c>
       <c r="D2" t="s">
         <v>340</v>
       </c>
-      <c r="E2" s="41" t="s">
+      <c r="E2" s="36" t="s">
         <v>281</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>341</v>
       </c>
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="35" t="s">
         <v>338</v>
       </c>
       <c r="D3" t="s">
         <v>342</v>
       </c>
-      <c r="E3" s="41" t="s">
+      <c r="E3" s="36" t="s">
         <v>283</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>343</v>
       </c>
-      <c r="B4" s="40" t="s">
+      <c r="B4" s="35" t="s">
         <v>338</v>
       </c>
       <c r="D4" t="s">
         <v>344</v>
       </c>
-      <c r="E4" s="41" t="s">
+      <c r="E4" s="36" t="s">
         <v>286</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="45.75">
+    <row r="5" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>345</v>
       </c>
-      <c r="B5" s="40" t="s">
+      <c r="B5" s="35" t="s">
         <v>346</v>
       </c>
       <c r="D5" t="s">
         <v>347</v>
       </c>
-      <c r="E5" s="41" t="s">
+      <c r="E5" s="36" t="s">
         <v>290</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="45.75">
+    <row r="6" spans="1:13" ht="48" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>348</v>
       </c>
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="35" t="s">
         <v>346</v>
       </c>
-      <c r="C6" s="40" t="s">
+      <c r="C6" s="35" t="s">
         <v>349</v>
       </c>
       <c r="D6" t="s">
         <v>350</v>
       </c>
-      <c r="E6" s="41" t="s">
+      <c r="E6" s="36" t="s">
         <v>293</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>351</v>
       </c>
-      <c r="B7" s="40" t="s">
+      <c r="B7" s="35" t="s">
         <v>352</v>
       </c>
       <c r="D7" t="s">
         <v>353</v>
       </c>
-      <c r="E7" s="41" t="s">
+      <c r="E7" s="36" t="s">
         <v>296</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>354</v>
       </c>
-      <c r="B8" s="40" t="s">
+      <c r="B8" s="35" t="s">
         <v>355</v>
       </c>
-      <c r="C8" s="40" t="s">
+      <c r="C8" s="35" t="s">
         <v>356</v>
       </c>
       <c r="D8" t="s">
         <v>357</v>
       </c>
-      <c r="E8" s="41" t="s">
+      <c r="E8" s="36" t="s">
         <v>299</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>358</v>
       </c>
-      <c r="B9" s="40" t="s">
+      <c r="B9" s="35" t="s">
         <v>359</v>
       </c>
       <c r="D9" t="s">
         <v>360</v>
       </c>
-      <c r="E9" s="41" t="s">
+      <c r="E9" s="36" t="s">
         <v>302</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>84</v>
       </c>
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="35" t="s">
         <v>361</v>
       </c>
       <c r="D10" t="s">
         <v>362</v>
       </c>
-      <c r="E10" s="41" t="s">
+      <c r="E10" s="36" t="s">
         <v>305</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="30.75">
+    <row r="11" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>363</v>
       </c>
-      <c r="B11" s="40" t="s">
+      <c r="B11" s="35" t="s">
         <v>364</v>
       </c>
-      <c r="C11" s="40" t="s">
+      <c r="C11" s="35" t="s">
         <v>365</v>
       </c>
       <c r="D11" t="s">
         <v>366</v>
       </c>
-      <c r="E11" s="41" t="s">
+      <c r="E11" s="36" t="s">
         <v>308</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="33">
+    <row r="12" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>367</v>
       </c>
-      <c r="B12" s="40" t="s">
+      <c r="B12" s="35" t="s">
         <v>368</v>
       </c>
-      <c r="C12" s="40" t="s">
+      <c r="C12" s="35" t="s">
         <v>369</v>
       </c>
       <c r="D12" t="s">
         <v>370</v>
       </c>
-      <c r="E12" s="41" t="s">
+      <c r="E12" s="36" t="s">
         <v>326</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="30.75">
+    <row r="13" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>371</v>
       </c>
-      <c r="B13" s="40" t="s">
+      <c r="B13" s="35" t="s">
         <v>372</v>
       </c>
-      <c r="C13" s="40" t="s">
+      <c r="C13" s="35" t="s">
         <v>373</v>
       </c>
       <c r="D13" t="s">
         <v>374</v>
       </c>
-      <c r="E13" s="41" t="s">
+      <c r="E13" s="36" t="s">
         <v>375</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="30.75">
+    <row r="14" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>376</v>
       </c>
-      <c r="B14" s="40" t="s">
+      <c r="B14" s="35" t="s">
         <v>377</v>
       </c>
       <c r="D14" t="s">
         <v>378</v>
       </c>
-      <c r="E14" s="41" t="s">
+      <c r="E14" s="36" t="s">
         <v>379</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="33">
+    <row r="15" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>380</v>
       </c>
-      <c r="B15" s="40" t="s">
+      <c r="B15" s="35" t="s">
         <v>381</v>
       </c>
       <c r="D15" t="s">
         <v>382</v>
       </c>
-      <c r="E15" s="41" t="s">
+      <c r="E15" s="36" t="s">
         <v>383</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>384</v>
       </c>
-      <c r="B16" s="40" t="s">
+      <c r="B16" s="35" t="s">
         <v>385</v>
       </c>
-      <c r="C16" s="40" t="s">
+      <c r="C16" s="35" t="s">
         <v>386</v>
       </c>
       <c r="D16" t="s">
         <v>387</v>
       </c>
-      <c r="E16" s="41" t="s">
+      <c r="E16" s="36" t="s">
         <v>388</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="17" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A19" s="14" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>389</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:M1">
-    <cfRule type="cellIs" dxfId="10" priority="5" operator="equal">
+  <conditionalFormatting sqref="A19">
+    <cfRule type="cellIs" dxfId="22" priority="4" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A19">
-    <cfRule type="cellIs" dxfId="9" priority="4" operator="equal">
+  <conditionalFormatting sqref="A1:M1">
+    <cfRule type="cellIs" dxfId="21" priority="5" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F16">
-    <cfRule type="containsText" dxfId="8" priority="3" operator="containsText" text="done">
-      <formula>NOT(ISERROR(SEARCH("done",F2)))</formula>
+    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
+      <formula>"N/A"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F16">
-    <cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="pending">
+    <cfRule type="containsText" dxfId="19" priority="2" operator="containsText" text="pending">
       <formula>NOT(ISERROR(SEARCH("pending",F2)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F16">
-    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
-      <formula>"N/A"</formula>
+    <cfRule type="containsText" dxfId="18" priority="3" operator="containsText" text="done">
+      <formula>NOT(ISERROR(SEARCH("done",F2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5941,65 +5517,307 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFAD67B6-A1D9-45BA-9B72-2E272EC150D4}">
-  <dimension ref="A1:L1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:L19"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.83203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="23" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="26.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="20" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="G1" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="H1" s="17" t="s">
+      <c r="H1" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="I1" s="18" t="s">
+      <c r="I1" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="J1" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="K1" s="17" t="s">
+      <c r="K1" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="L1" s="18" t="s">
+      <c r="L1" s="15" t="s">
         <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>426</v>
+      </c>
+      <c r="D2" t="s">
+        <v>427</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>428</v>
+      </c>
+      <c r="D3" t="s">
+        <v>429</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>430</v>
+      </c>
+      <c r="D4" t="s">
+        <v>431</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>341</v>
+      </c>
+      <c r="D5" t="s">
+        <v>432</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D6" t="s">
+        <v>433</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7" t="s">
+        <v>434</v>
+      </c>
+      <c r="E7">
+        <v>6</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="80" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>435</v>
+      </c>
+      <c r="B8" s="35" t="s">
+        <v>364</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>445</v>
+      </c>
+      <c r="D8" t="s">
+        <v>436</v>
+      </c>
+      <c r="E8">
+        <v>7</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="80" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>367</v>
+      </c>
+      <c r="B9" s="35" t="s">
+        <v>368</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>445</v>
+      </c>
+      <c r="D9" t="s">
+        <v>437</v>
+      </c>
+      <c r="E9">
+        <v>8</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="80" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>438</v>
+      </c>
+      <c r="B10" s="35" t="s">
+        <v>364</v>
+      </c>
+      <c r="C10" s="35" t="s">
+        <v>445</v>
+      </c>
+      <c r="D10" t="s">
+        <v>439</v>
+      </c>
+      <c r="E10">
+        <v>9</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="112" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>380</v>
+      </c>
+      <c r="B11" s="35" t="s">
+        <v>444</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>446</v>
+      </c>
+      <c r="D11" t="s">
+        <v>440</v>
+      </c>
+      <c r="E11">
+        <v>10</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="80" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>441</v>
+      </c>
+      <c r="B12" s="35" t="s">
+        <v>444</v>
+      </c>
+      <c r="C12" s="35" t="s">
+        <v>445</v>
+      </c>
+      <c r="D12" t="s">
+        <v>442</v>
+      </c>
+      <c r="E12">
+        <v>11</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>384</v>
+      </c>
+      <c r="D13" t="s">
+        <v>443</v>
+      </c>
+      <c r="E13">
+        <v>12</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="F14" s="1"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A15" s="14" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>389</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:L1">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="5" operator="equal">
       <formula>"N/A"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A15">
+    <cfRule type="cellIs" dxfId="16" priority="4" operator="equal">
+      <formula>"N/A"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F14">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>"N/A"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="pending">
+      <formula>NOT(ISERROR(SEARCH("pending",F2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="done">
+      <formula>NOT(ISERROR(SEARCH("done",F2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6009,207 +5827,406 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF58CD2C-5CA3-403D-99C4-85A5E9258B53}">
   <dimension ref="A1:M23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.28515625" customWidth="1"/>
-    <col min="2" max="2" width="30.85546875" customWidth="1"/>
-    <col min="3" max="3" width="29.28515625" customWidth="1"/>
-    <col min="4" max="4" width="53.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.33203125" customWidth="1"/>
+    <col min="2" max="2" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="29.33203125" customWidth="1"/>
+    <col min="4" max="4" width="53.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.83203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="23" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="26.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="26.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.33203125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="20" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="34" t="s">
         <v>279</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="G1" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="H1" s="17" t="s">
+      <c r="G1" s="14" t="s">
+        <v>390</v>
+      </c>
+      <c r="H1" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="I1" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="J1" s="18" t="s">
+      <c r="J1" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="K1" s="17" t="s">
+      <c r="K1" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="L1" s="17" t="s">
+      <c r="L1" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="M1" s="18" t="s">
+      <c r="M1" s="15" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="1"/>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="1"/>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="1"/>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="B5" s="40"/>
-      <c r="C5" s="40"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="1"/>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="B6" s="40"/>
-      <c r="C6" s="40"/>
-      <c r="E6" s="41"/>
-      <c r="F6" s="1"/>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="B7" s="40"/>
-      <c r="C7" s="40"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="1"/>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="B8" s="40"/>
-      <c r="C8" s="40"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="1"/>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="B9" s="40"/>
-      <c r="C9" s="40"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="1"/>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="B10" s="40"/>
-      <c r="C10" s="40"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="1"/>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="B11" s="40"/>
-      <c r="C11" s="40"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="1"/>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="B12" s="40"/>
-      <c r="C12" s="40"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="1"/>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="B13" s="40"/>
-      <c r="C13" s="40"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="1"/>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="B14" s="40"/>
-      <c r="C14" s="40"/>
-      <c r="E14" s="41"/>
-      <c r="F14" s="1"/>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="B15" s="40"/>
-      <c r="C15" s="40"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="1"/>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="B16" s="40"/>
-      <c r="C16" s="40"/>
-      <c r="E16" s="41"/>
-      <c r="F16" s="1"/>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="B17" s="40"/>
-      <c r="C17" s="40"/>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="B18" s="40"/>
-      <c r="C18" s="40"/>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="17"/>
-      <c r="B19" s="40"/>
-      <c r="C19" s="40"/>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="B20" s="40"/>
-      <c r="C20" s="40"/>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="B21" s="40"/>
-      <c r="C21" s="40"/>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="B22" s="40"/>
-      <c r="C22" s="40"/>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="B23" s="40"/>
-      <c r="C23" s="40"/>
+    <row r="2" spans="1:13" ht="32" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>391</v>
+      </c>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35" t="s">
+        <v>425</v>
+      </c>
+      <c r="D2" t="s">
+        <v>392</v>
+      </c>
+      <c r="E2" s="36">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>393</v>
+      </c>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" t="s">
+        <v>394</v>
+      </c>
+      <c r="E3" s="36">
+        <v>2</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>395</v>
+      </c>
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" t="s">
+        <v>396</v>
+      </c>
+      <c r="E4" s="36">
+        <v>3</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
+      <c r="D5" t="s">
+        <v>397</v>
+      </c>
+      <c r="E5" s="36">
+        <v>4</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" s="35"/>
+      <c r="C6" s="35"/>
+      <c r="D6" t="s">
+        <v>398</v>
+      </c>
+      <c r="E6" s="36">
+        <v>5</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="32" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>399</v>
+      </c>
+      <c r="B7" s="35" t="s">
+        <v>364</v>
+      </c>
+      <c r="C7" s="35" t="s">
+        <v>418</v>
+      </c>
+      <c r="D7" t="s">
+        <v>400</v>
+      </c>
+      <c r="E7" s="36">
+        <v>6</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>401</v>
+      </c>
+      <c r="B8" s="35" t="s">
+        <v>419</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>418</v>
+      </c>
+      <c r="D8" t="s">
+        <v>402</v>
+      </c>
+      <c r="E8" s="36">
+        <v>7</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="32" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>367</v>
+      </c>
+      <c r="B9" s="35" t="s">
+        <v>368</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>418</v>
+      </c>
+      <c r="D9" t="s">
+        <v>403</v>
+      </c>
+      <c r="E9" s="36">
+        <v>8</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>404</v>
+      </c>
+      <c r="B10" s="35"/>
+      <c r="C10" s="35" t="s">
+        <v>418</v>
+      </c>
+      <c r="D10" t="s">
+        <v>405</v>
+      </c>
+      <c r="E10" s="36">
+        <v>9</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="32" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>380</v>
+      </c>
+      <c r="B11" s="35" t="s">
+        <v>381</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>418</v>
+      </c>
+      <c r="D11" t="s">
+        <v>406</v>
+      </c>
+      <c r="E11" s="36">
+        <v>10</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>407</v>
+      </c>
+      <c r="C12" s="35" t="s">
+        <v>420</v>
+      </c>
+      <c r="D12" t="s">
+        <v>408</v>
+      </c>
+      <c r="E12" s="36">
+        <v>11</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>409</v>
+      </c>
+      <c r="C13" s="35" t="s">
+        <v>421</v>
+      </c>
+      <c r="D13" t="s">
+        <v>410</v>
+      </c>
+      <c r="E13" s="36">
+        <v>12</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>411</v>
+      </c>
+      <c r="C14" s="35" t="s">
+        <v>423</v>
+      </c>
+      <c r="D14" t="s">
+        <v>412</v>
+      </c>
+      <c r="E14" s="36">
+        <v>13</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="32" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>413</v>
+      </c>
+      <c r="C15" s="35" t="s">
+        <v>422</v>
+      </c>
+      <c r="D15" t="s">
+        <v>414</v>
+      </c>
+      <c r="E15" s="36">
+        <v>14</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>415</v>
+      </c>
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
+      <c r="D16" t="s">
+        <v>416</v>
+      </c>
+      <c r="E16" s="36">
+        <v>15</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>384</v>
+      </c>
+      <c r="B17" s="35"/>
+      <c r="C17" s="35" t="s">
+        <v>424</v>
+      </c>
+      <c r="D17" t="s">
+        <v>417</v>
+      </c>
+      <c r="E17">
+        <v>16</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B18" s="35"/>
+      <c r="C18" s="35"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="14" t="s">
+        <v>309</v>
+      </c>
+      <c r="B19" s="35"/>
+      <c r="C19" s="35"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>310</v>
+      </c>
+      <c r="B20" s="35"/>
+      <c r="C20" s="35"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>311</v>
+      </c>
+      <c r="B21" s="35"/>
+      <c r="C21" s="35"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>312</v>
+      </c>
+      <c r="B22" s="35"/>
+      <c r="C22" s="35"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>389</v>
+      </c>
+      <c r="B23" s="35"/>
+      <c r="C23" s="35"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:M1">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+  <phoneticPr fontId="8" type="noConversion"/>
+  <conditionalFormatting sqref="A19">
+    <cfRule type="cellIs" dxfId="10" priority="7" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A19">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+  <conditionalFormatting sqref="A1:M1">
+    <cfRule type="cellIs" dxfId="9" priority="8" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F16">
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="done">
-      <formula>NOT(ISERROR(SEARCH("done",F2)))</formula>
+  <conditionalFormatting sqref="F2:F17">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
+      <formula>"N/A"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F16">
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="pending">
+    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="pending">
       <formula>NOT(ISERROR(SEARCH("pending",F2)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F16">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>"N/A"</formula>
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="done">
+      <formula>NOT(ISERROR(SEARCH("done",F2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6219,144 +6236,132 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8053823-620C-4DEC-8B9B-441EC38E5233}">
   <dimension ref="A1:M13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="23" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="17" customFormat="1">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="G1" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="H1" s="17" t="s">
+      <c r="H1" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="I1" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="J1" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="K1" s="18" t="s">
+      <c r="K1" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="L1" s="17" t="s">
+      <c r="L1" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="M1" s="18" t="s">
+      <c r="M1" s="15" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:13" s="12" customFormat="1">
-      <c r="A2" s="12" t="s">
+    <row r="2" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="E2" s="13"/>
-      <c r="F2" s="14"/>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="3" t="s">
+      <c r="E2" s="10"/>
+      <c r="F2" s="11"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>76</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" t="s">
         <v>77</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" t="s">
         <v>78</v>
       </c>
       <c r="D3" t="s">
         <v>79</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="3" t="s">
+      <c r="E3" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>76</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" t="s">
         <v>77</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" t="s">
         <v>81</v>
       </c>
       <c r="D4" t="s">
         <v>82</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-    </row>
-    <row r="5" spans="1:13" s="12" customFormat="1">
-      <c r="A5" s="12" t="s">
+      <c r="E4" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="E5" s="13"/>
-      <c r="F5" s="14"/>
-    </row>
-    <row r="6" spans="1:13" s="12" customFormat="1">
-      <c r="A6" s="12" t="s">
+      <c r="E5" s="10"/>
+      <c r="F5" s="11"/>
+    </row>
+    <row r="6" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="E6" s="13"/>
-      <c r="F6" s="14"/>
-    </row>
-    <row r="7" spans="1:13">
+      <c r="E6" s="10"/>
+      <c r="F6" s="11"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>85</v>
       </c>
@@ -6369,14 +6374,14 @@
       <c r="D7" t="s">
         <v>88</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="4" t="s">
         <v>47</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>89</v>
       </c>
@@ -6389,14 +6394,14 @@
       <c r="D8" t="s">
         <v>91</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="4" t="s">
         <v>47</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>92</v>
       </c>
@@ -6409,14 +6414,14 @@
       <c r="D9" t="s">
         <v>94</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="4" t="s">
         <v>47</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>95</v>
       </c>
@@ -6429,17 +6434,17 @@
       <c r="D10" t="s">
         <v>97</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="4" t="s">
         <v>47</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="H10" s="10" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
+      <c r="H10" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>98</v>
       </c>
@@ -6452,17 +6457,17 @@
       <c r="D11" t="s">
         <v>101</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="4" t="s">
         <v>47</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="H11" s="10" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
+      <c r="H11" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>102</v>
       </c>
@@ -6475,43 +6480,41 @@
       <c r="D12" t="s">
         <v>105</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="4" t="s">
         <v>47</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="H12" s="10" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
+      <c r="H12" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="F13" s="1"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:E12">
-    <cfRule type="containsText" dxfId="108" priority="5" operator="containsText" text="pending">
-      <formula>NOT(ISERROR(SEARCH("pending",E2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B2:B12">
-    <cfRule type="containsText" dxfId="107" priority="4" operator="containsText" text="none">
+    <cfRule type="containsText" dxfId="84" priority="4" operator="containsText" text="none">
       <formula>NOT(ISERROR(SEARCH("none",B2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C4">
-    <cfRule type="containsText" dxfId="106" priority="3" operator="containsText" text="none">
+    <cfRule type="containsText" dxfId="83" priority="3" operator="containsText" text="none">
       <formula>NOT(ISERROR(SEARCH("none",C2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F7:F13">
-    <cfRule type="containsText" dxfId="105" priority="2" operator="containsText" text="done">
-      <formula>NOT(ISERROR(SEARCH("done",F7)))</formula>
+  <conditionalFormatting sqref="E2:E12">
+    <cfRule type="containsText" dxfId="82" priority="5" operator="containsText" text="pending">
+      <formula>NOT(ISERROR(SEARCH("pending",E2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:F13">
-    <cfRule type="containsText" dxfId="104" priority="1" operator="containsText" text="pending">
+    <cfRule type="containsText" dxfId="81" priority="1" operator="containsText" text="pending">
       <formula>NOT(ISERROR(SEARCH("pending",F7)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="80" priority="2" operator="containsText" text="done">
+      <formula>NOT(ISERROR(SEARCH("done",F7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6521,88 +6524,88 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{378E61BE-8FF8-4B92-A3CC-662896958287}">
   <dimension ref="A1:M11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="33.140625" customWidth="1"/>
-    <col min="2" max="2" width="29.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32.42578125" customWidth="1"/>
-    <col min="5" max="5" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.1640625" customWidth="1"/>
+    <col min="2" max="2" width="29.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.5" customWidth="1"/>
+    <col min="5" max="5" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="17" customFormat="1">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="G1" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="H1" s="17" t="s">
+      <c r="H1" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="I1" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="J1" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="K1" s="18" t="s">
+      <c r="K1" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="L1" s="17" t="s">
+      <c r="L1" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="M1" s="18" t="s">
+      <c r="M1" s="15" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:13" s="12" customFormat="1">
-      <c r="A2" s="12" t="s">
+    <row r="2" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="E2" s="13"/>
-      <c r="F2" s="14"/>
-    </row>
-    <row r="3" spans="1:13" s="3" customFormat="1">
-      <c r="A3" s="3" t="s">
+      <c r="E2" s="10"/>
+      <c r="F2" s="11"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>76</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" t="s">
         <v>77</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" t="s">
         <v>106</v>
       </c>
       <c r="D3" t="s">
         <v>107</v>
       </c>
-      <c r="E3" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="F3" s="9" t="s">
+      <c r="E3" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>80</v>
       </c>
       <c r="H3" t="s">
@@ -6612,7 +6615,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>108</v>
       </c>
@@ -6625,7 +6628,7 @@
       <c r="D4" t="s">
         <v>111</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="7" t="s">
         <v>47</v>
       </c>
       <c r="F4" s="1" t="s">
@@ -6641,7 +6644,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>85</v>
       </c>
@@ -6654,7 +6657,7 @@
       <c r="D5" t="s">
         <v>115</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="7" t="s">
         <v>47</v>
       </c>
       <c r="F5" s="1" t="s">
@@ -6664,7 +6667,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>89</v>
       </c>
@@ -6677,7 +6680,7 @@
       <c r="D6" t="s">
         <v>117</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="7" t="s">
         <v>47</v>
       </c>
       <c r="F6" s="1" t="s">
@@ -6687,7 +6690,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>92</v>
       </c>
@@ -6700,14 +6703,14 @@
       <c r="D7" t="s">
         <v>119</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="7" t="s">
         <v>47</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>95</v>
       </c>
@@ -6720,14 +6723,14 @@
       <c r="D8" t="s">
         <v>120</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="7" t="s">
         <v>47</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>121</v>
       </c>
@@ -6740,7 +6743,7 @@
       <c r="D9" t="s">
         <v>122</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="7" t="s">
         <v>47</v>
       </c>
       <c r="F9" s="1" t="s">
@@ -6753,7 +6756,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>98</v>
       </c>
@@ -6766,7 +6769,7 @@
       <c r="D10" t="s">
         <v>124</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="7" t="s">
         <v>47</v>
       </c>
       <c r="F10" s="1" t="s">
@@ -6779,7 +6782,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>102</v>
       </c>
@@ -6809,39 +6812,34 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:E10 F3">
-    <cfRule type="containsText" dxfId="103" priority="7" operator="containsText" text="pending">
-      <formula>NOT(ISERROR(SEARCH("pending",E2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B2:B11">
-    <cfRule type="containsText" dxfId="102" priority="6" operator="containsText" text="none">
+    <cfRule type="containsText" dxfId="79" priority="6" operator="containsText" text="none">
       <formula>NOT(ISERROR(SEARCH("none",B2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C3">
-    <cfRule type="containsText" dxfId="101" priority="5" operator="containsText" text="none">
+    <cfRule type="containsText" dxfId="78" priority="5" operator="containsText" text="none">
       <formula>NOT(ISERROR(SEARCH("none",C2)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E11">
+    <cfRule type="containsText" dxfId="77" priority="3" operator="containsText" text="pending">
+      <formula>NOT(ISERROR(SEARCH("pending",E2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E11">
-    <cfRule type="containsText" dxfId="100" priority="4" operator="containsText" text="done">
+    <cfRule type="containsText" dxfId="76" priority="4" operator="containsText" text="done">
       <formula>NOT(ISERROR(SEARCH("done",E11)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E11">
-    <cfRule type="containsText" dxfId="99" priority="3" operator="containsText" text="pending">
-      <formula>NOT(ISERROR(SEARCH("pending",E11)))</formula>
+  <conditionalFormatting sqref="F3:F11">
+    <cfRule type="containsText" dxfId="75" priority="1" operator="containsText" text="pending">
+      <formula>NOT(ISERROR(SEARCH("pending",F3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F11">
-    <cfRule type="containsText" dxfId="98" priority="2" operator="containsText" text="done">
+    <cfRule type="containsText" dxfId="74" priority="2" operator="containsText" text="done">
       <formula>NOT(ISERROR(SEARCH("done",F4)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4:F11">
-    <cfRule type="containsText" dxfId="97" priority="1" operator="containsText" text="pending">
-      <formula>NOT(ISERROR(SEARCH("pending",F4)))</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
@@ -6855,65 +6853,65 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3915B174-373E-4B56-947D-B710712BD39F}">
   <dimension ref="A1:Q14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="23" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="17" customFormat="1">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:17" s="14" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="G1" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="H1" s="17" t="s">
+      <c r="H1" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="I1" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="J1" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="K1" s="18" t="s">
+      <c r="K1" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="L1" s="17" t="s">
+      <c r="L1" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="M1" s="18" t="s">
+      <c r="M1" s="15" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:17" s="15" customFormat="1">
+    <row r="2" spans="1:17" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>83</v>
       </c>
@@ -6926,7 +6924,7 @@
       <c r="D2" t="s">
         <v>127</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="4">
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -6948,7 +6946,7 @@
       <c r="P2"/>
       <c r="Q2"/>
     </row>
-    <row r="3" spans="1:17" s="7" customFormat="1">
+    <row r="3" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>84</v>
       </c>
@@ -6961,7 +6959,7 @@
       <c r="D3" t="s">
         <v>129</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="4">
         <v>2</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -6983,7 +6981,7 @@
       <c r="P3"/>
       <c r="Q3"/>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>130</v>
       </c>
@@ -6996,14 +6994,14 @@
       <c r="D4" t="s">
         <v>131</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="4">
         <v>3</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>132</v>
       </c>
@@ -7016,14 +7014,14 @@
       <c r="D5" t="s">
         <v>134</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="4">
         <v>4</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>89</v>
       </c>
@@ -7036,14 +7034,14 @@
       <c r="D6" t="s">
         <v>135</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="4">
         <v>5</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>85</v>
       </c>
@@ -7056,14 +7054,14 @@
       <c r="D7" t="s">
         <v>136</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="4">
         <v>6</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>92</v>
       </c>
@@ -7076,14 +7074,14 @@
       <c r="D8" t="s">
         <v>137</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="4">
         <v>7</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>95</v>
       </c>
@@ -7096,7 +7094,7 @@
       <c r="D9" t="s">
         <v>138</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="4">
         <v>8</v>
       </c>
       <c r="F9" s="1" t="s">
@@ -7109,7 +7107,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>121</v>
       </c>
@@ -7122,7 +7120,7 @@
       <c r="D10" t="s">
         <v>139</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="4">
         <v>9</v>
       </c>
       <c r="F10" s="1" t="s">
@@ -7135,7 +7133,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>98</v>
       </c>
@@ -7148,7 +7146,7 @@
       <c r="D11" t="s">
         <v>140</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="4">
         <v>10</v>
       </c>
       <c r="F11" s="1" t="s">
@@ -7161,7 +7159,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>102</v>
       </c>
@@ -7174,7 +7172,7 @@
       <c r="D12" t="s">
         <v>141</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="4">
         <v>11</v>
       </c>
       <c r="F12" s="1" t="s">
@@ -7187,61 +7185,52 @@
         <v>80</v>
       </c>
     </row>
-    <row r="13" spans="1:17">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
         <v>76</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" t="s">
         <v>77</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" t="s">
         <v>106</v>
       </c>
       <c r="D13" t="s">
         <v>142</v>
       </c>
-      <c r="E13" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="G13" s="3"/>
+      <c r="E13" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>80</v>
+      </c>
       <c r="H13" t="s">
         <v>80</v>
       </c>
       <c r="I13" t="s">
         <v>80</v>
       </c>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3"/>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17">
-      <c r="A14" s="15" t="s">
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A14" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="15"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="15"/>
-      <c r="O14" s="15"/>
-      <c r="P14" s="15"/>
-      <c r="Q14" s="15"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="12"/>
+      <c r="M14" s="12"/>
+      <c r="N14" s="12"/>
+      <c r="O14" s="12"/>
+      <c r="P14" s="12"/>
+      <c r="Q14" s="12"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:Q1" xr:uid="{3915B174-373E-4B56-947D-B710712BD39F}">
@@ -7249,54 +7238,37 @@
       <sortCondition ref="E1"/>
     </sortState>
   </autoFilter>
+  <conditionalFormatting sqref="B2:B14">
+    <cfRule type="containsText" dxfId="73" priority="6" operator="containsText" text="none">
+      <formula>NOT(ISERROR(SEARCH("none",B2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C3">
+    <cfRule type="containsText" dxfId="72" priority="5" operator="containsText" text="none">
+      <formula>NOT(ISERROR(SEARCH("none",C3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:F2">
+    <cfRule type="containsText" dxfId="71" priority="10" operator="containsText" text="none">
+      <formula>NOT(ISERROR(SEARCH("none",C2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E4:E14">
-    <cfRule type="containsText" dxfId="96" priority="12" operator="containsText" text="pending">
+    <cfRule type="containsText" dxfId="70" priority="12" operator="containsText" text="pending">
       <formula>NOT(ISERROR(SEARCH("pending",E4)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2 B4:B14">
-    <cfRule type="containsText" dxfId="95" priority="11" operator="containsText" text="none">
-      <formula>NOT(ISERROR(SEARCH("none",B2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C2:F2">
-    <cfRule type="containsText" dxfId="94" priority="10" operator="containsText" text="none">
-      <formula>NOT(ISERROR(SEARCH("none",C2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="E3:F3">
-    <cfRule type="containsText" dxfId="93" priority="7" operator="containsText" text="pending">
+    <cfRule type="containsText" dxfId="69" priority="7" operator="containsText" text="pending">
       <formula>NOT(ISERROR(SEARCH("pending",E3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B3">
-    <cfRule type="containsText" dxfId="92" priority="6" operator="containsText" text="none">
-      <formula>NOT(ISERROR(SEARCH("none",B3)))</formula>
+  <conditionalFormatting sqref="F2:F14">
+    <cfRule type="containsText" dxfId="68" priority="1" operator="containsText" text="pending">
+      <formula>NOT(ISERROR(SEARCH("pending",F2)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C3">
-    <cfRule type="containsText" dxfId="91" priority="5" operator="containsText" text="none">
-      <formula>NOT(ISERROR(SEARCH("none",C3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F14">
-    <cfRule type="containsText" dxfId="90" priority="4" operator="containsText" text="done">
-      <formula>NOT(ISERROR(SEARCH("done",F14)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F14">
-    <cfRule type="containsText" dxfId="89" priority="3" operator="containsText" text="pending">
-      <formula>NOT(ISERROR(SEARCH("pending",F14)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F13">
-    <cfRule type="containsText" dxfId="88" priority="2" operator="containsText" text="done">
+    <cfRule type="containsText" dxfId="67" priority="2" operator="containsText" text="done">
       <formula>NOT(ISERROR(SEARCH("done",F2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F13">
-    <cfRule type="containsText" dxfId="87" priority="1" operator="containsText" text="pending">
-      <formula>NOT(ISERROR(SEARCH("pending",F2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7306,191 +7278,169 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CD6DD0E-17B5-4DCC-9BA6-3F1F0AE952F1}">
   <dimension ref="A1:L14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="40.5703125" customWidth="1"/>
-    <col min="2" max="2" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="40.5" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="23" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="17" customFormat="1">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:12" s="14" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="G1" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="H1" s="17" t="s">
+      <c r="H1" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="I1" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="J1" s="18" t="s">
+      <c r="J1" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="K1" s="17" t="s">
+      <c r="K1" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="L1" s="18" t="s">
+      <c r="L1" s="15" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>75</v>
       </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="10"/>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="D2" s="3"/>
+      <c r="E2" s="1"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>83</v>
       </c>
-      <c r="D3" s="4"/>
+      <c r="D3" s="3"/>
       <c r="E3" s="1"/>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>84</v>
       </c>
-      <c r="D4" s="4"/>
+      <c r="D4" s="3"/>
       <c r="E4" s="1"/>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>85</v>
       </c>
-      <c r="D5" s="4"/>
+      <c r="D5" s="3"/>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>89</v>
       </c>
-      <c r="D6" s="4"/>
+      <c r="D6" s="3"/>
       <c r="E6" s="1"/>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>145</v>
       </c>
-      <c r="D7" s="4"/>
+      <c r="D7" s="3"/>
       <c r="E7" s="1"/>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>95</v>
       </c>
-      <c r="D8" s="4"/>
+      <c r="D8" s="3"/>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>146</v>
       </c>
-      <c r="D9" s="4"/>
+      <c r="D9" s="3"/>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>147</v>
       </c>
-      <c r="D10" s="4"/>
+      <c r="D10" s="3"/>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>148</v>
       </c>
-      <c r="D11" s="4"/>
+      <c r="D11" s="3"/>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>149</v>
       </c>
-      <c r="D12" s="4"/>
+      <c r="D12" s="3"/>
       <c r="E12" s="1"/>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>150</v>
       </c>
-      <c r="D13" s="4"/>
+      <c r="D13" s="3"/>
       <c r="E13" s="1"/>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>102</v>
       </c>
-      <c r="D14" s="5"/>
+      <c r="D14" s="4"/>
       <c r="E14" s="1"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E3:E13">
-    <cfRule type="containsText" dxfId="86" priority="8" operator="containsText" text="done">
-      <formula>NOT(ISERROR(SEARCH("done",E3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E3:E13">
-    <cfRule type="containsText" dxfId="85" priority="7" operator="containsText" text="pending">
-      <formula>NOT(ISERROR(SEARCH("pending",E3)))</formula>
+  <conditionalFormatting sqref="B2:B14">
+    <cfRule type="containsText" dxfId="66" priority="3" operator="containsText" text="none">
+      <formula>NOT(ISERROR(SEARCH("none",B2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="containsText" dxfId="84" priority="6" operator="containsText" text="pending">
+    <cfRule type="containsText" dxfId="65" priority="6" operator="containsText" text="pending">
       <formula>NOT(ISERROR(SEARCH("pending",D14)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B12">
-    <cfRule type="containsText" dxfId="83" priority="5" operator="containsText" text="none">
-      <formula>NOT(ISERROR(SEARCH("none",B2)))</formula>
+  <conditionalFormatting sqref="E3:E14">
+    <cfRule type="containsText" dxfId="64" priority="1" operator="containsText" text="pending">
+      <formula>NOT(ISERROR(SEARCH("pending",E3)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B14">
-    <cfRule type="containsText" dxfId="82" priority="4" operator="containsText" text="none">
-      <formula>NOT(ISERROR(SEARCH("none",B14)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B13">
-    <cfRule type="containsText" dxfId="81" priority="3" operator="containsText" text="none">
-      <formula>NOT(ISERROR(SEARCH("none",B13)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E14">
-    <cfRule type="containsText" dxfId="80" priority="2" operator="containsText" text="done">
-      <formula>NOT(ISERROR(SEARCH("done",E14)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E14">
-    <cfRule type="containsText" dxfId="79" priority="1" operator="containsText" text="pending">
-      <formula>NOT(ISERROR(SEARCH("pending",E14)))</formula>
+    <cfRule type="containsText" dxfId="63" priority="2" operator="containsText" text="done">
+      <formula>NOT(ISERROR(SEARCH("done",E3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7500,76 +7450,76 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5467EDD7-48C1-42F4-82EE-822B31078C75}">
   <dimension ref="A1:M13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.28515625" customWidth="1"/>
-    <col min="8" max="8" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.33203125" customWidth="1"/>
+    <col min="8" max="8" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="17" customFormat="1">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="G1" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="H1" s="17" t="s">
+      <c r="H1" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="I1" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="J1" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="K1" s="18" t="s">
+      <c r="K1" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="L1" s="17" t="s">
+      <c r="L1" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="M1" s="18" t="s">
+      <c r="M1" s="15" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="16"/>
+      <c r="B2" s="13"/>
       <c r="C2" t="s">
         <v>104</v>
       </c>
       <c r="D2" t="s">
         <v>151</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>47</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -7582,7 +7532,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>89</v>
       </c>
@@ -7595,14 +7545,14 @@
       <c r="D3" t="s">
         <v>153</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="4">
         <v>1</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>83</v>
       </c>
@@ -7615,7 +7565,7 @@
       <c r="D4" t="s">
         <v>155</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="4">
         <v>2</v>
       </c>
       <c r="F4" s="1" t="s">
@@ -7628,7 +7578,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>84</v>
       </c>
@@ -7641,7 +7591,7 @@
       <c r="D5" t="s">
         <v>157</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="4">
         <v>3</v>
       </c>
       <c r="F5" s="1" t="s">
@@ -7654,7 +7604,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>85</v>
       </c>
@@ -7667,14 +7617,14 @@
       <c r="D6" t="s">
         <v>159</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="4">
         <v>4</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>132</v>
       </c>
@@ -7687,14 +7637,14 @@
       <c r="D7" t="s">
         <v>161</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="4">
         <v>7</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>92</v>
       </c>
@@ -7707,14 +7657,14 @@
       <c r="D8" t="s">
         <v>163</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="4">
         <v>6</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>130</v>
       </c>
@@ -7727,14 +7677,14 @@
       <c r="D9" t="s">
         <v>165</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="4">
         <v>5</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>95</v>
       </c>
@@ -7747,7 +7697,7 @@
       <c r="D10" t="s">
         <v>167</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="4">
         <v>9</v>
       </c>
       <c r="F10" s="1" t="s">
@@ -7760,7 +7710,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>150</v>
       </c>
@@ -7773,7 +7723,7 @@
       <c r="D11" t="s">
         <v>170</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="4">
         <v>8</v>
       </c>
       <c r="F11" s="1" t="s">
@@ -7789,7 +7739,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>172</v>
       </c>
@@ -7802,7 +7752,7 @@
       <c r="D12" t="s">
         <v>174</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="4" t="s">
         <v>47</v>
       </c>
       <c r="F12" s="1" t="s">
@@ -7815,7 +7765,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>175</v>
       </c>
@@ -7825,10 +7775,10 @@
       <c r="C13" t="s">
         <v>176</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="4" t="s">
         <v>47</v>
       </c>
       <c r="F13" s="1" t="s">
@@ -7842,54 +7792,19 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:E13">
-    <cfRule type="containsText" dxfId="78" priority="19" operator="containsText" text="pending">
+  <conditionalFormatting sqref="B2:B13">
+    <cfRule type="containsText" dxfId="62" priority="11" operator="containsText" text="none">
+      <formula>NOT(ISERROR(SEARCH("none",B2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:F13">
+    <cfRule type="containsText" dxfId="61" priority="1" operator="containsText" text="pending">
       <formula>NOT(ISERROR(SEARCH("pending",E2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B3 B6 B8 B11">
-    <cfRule type="containsText" dxfId="77" priority="18" operator="containsText" text="none">
-      <formula>NOT(ISERROR(SEARCH("none",B2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B12">
-    <cfRule type="containsText" dxfId="76" priority="17" operator="containsText" text="none">
-      <formula>NOT(ISERROR(SEARCH("none",B12)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B13">
-    <cfRule type="containsText" dxfId="75" priority="16" operator="containsText" text="none">
-      <formula>NOT(ISERROR(SEARCH("none",B13)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B4:B5">
-    <cfRule type="containsText" dxfId="74" priority="14" operator="containsText" text="none">
-      <formula>NOT(ISERROR(SEARCH("none",B4)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B7">
-    <cfRule type="containsText" dxfId="73" priority="13" operator="containsText" text="none">
-      <formula>NOT(ISERROR(SEARCH("none",B7)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B10">
-    <cfRule type="containsText" dxfId="72" priority="12" operator="containsText" text="none">
-      <formula>NOT(ISERROR(SEARCH("none",B10)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B9">
-    <cfRule type="containsText" dxfId="71" priority="11" operator="containsText" text="none">
-      <formula>NOT(ISERROR(SEARCH("none",B9)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F2:F13">
-    <cfRule type="containsText" dxfId="70" priority="2" operator="containsText" text="done">
+    <cfRule type="containsText" dxfId="60" priority="2" operator="containsText" text="done">
       <formula>NOT(ISERROR(SEARCH("done",F2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F13">
-    <cfRule type="containsText" dxfId="69" priority="1" operator="containsText" text="pending">
-      <formula>NOT(ISERROR(SEARCH("pending",F2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7899,65 +7814,65 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9F1C1CB-FD8B-48E8-98DF-2BE8760636CA}">
   <dimension ref="A1:M13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" customWidth="1"/>
-    <col min="8" max="8" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.6640625" customWidth="1"/>
+    <col min="8" max="8" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="17" customFormat="1">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="G1" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="H1" s="17" t="s">
+      <c r="H1" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="I1" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="J1" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="K1" s="18" t="s">
+      <c r="K1" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="L1" s="17" t="s">
+      <c r="L1" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="M1" s="18" t="s">
+      <c r="M1" s="15" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>83</v>
       </c>
@@ -7970,7 +7885,7 @@
       <c r="D2" t="s">
         <v>178</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="3">
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -7986,7 +7901,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>84</v>
       </c>
@@ -7999,7 +7914,7 @@
       <c r="D3" t="s">
         <v>180</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="3">
         <v>2</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -8015,7 +7930,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>85</v>
       </c>
@@ -8028,7 +7943,7 @@
       <c r="D4" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="3">
         <v>3</v>
       </c>
       <c r="F4" s="1" t="s">
@@ -8038,7 +7953,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>89</v>
       </c>
@@ -8051,7 +7966,7 @@
       <c r="D5" t="s">
         <v>182</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="3">
         <v>4</v>
       </c>
       <c r="F5" s="1" t="s">
@@ -8061,7 +7976,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>132</v>
       </c>
@@ -8074,7 +7989,7 @@
       <c r="D6" t="s">
         <v>183</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="3">
         <v>5</v>
       </c>
       <c r="F6" s="1" t="s">
@@ -8084,7 +7999,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>130</v>
       </c>
@@ -8097,7 +8012,7 @@
       <c r="D7" t="s">
         <v>184</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="3">
         <v>6</v>
       </c>
       <c r="F7" s="1" t="s">
@@ -8107,7 +8022,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>102</v>
       </c>
@@ -8120,7 +8035,7 @@
       <c r="D8" t="s">
         <v>185</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="4" t="s">
         <v>47</v>
       </c>
       <c r="F8" s="1" t="s">
@@ -8136,70 +8051,43 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="F9" s="1"/>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="F10" s="1"/>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="F11" s="1"/>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="F12" s="1"/>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="F13" s="1"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E8 E2:E3">
-    <cfRule type="containsText" dxfId="68" priority="13" operator="containsText" text="pending">
+  <conditionalFormatting sqref="B2:B8">
+    <cfRule type="containsText" dxfId="59" priority="5" operator="containsText" text="none">
+      <formula>NOT(ISERROR(SEARCH("none",B2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E3 E8">
+    <cfRule type="containsText" dxfId="58" priority="13" operator="containsText" text="pending">
       <formula>NOT(ISERROR(SEARCH("pending",E2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J9">
-    <cfRule type="containsText" dxfId="67" priority="11" operator="containsText" text="none">
-      <formula>NOT(ISERROR(SEARCH("none",J2)))</formula>
+  <conditionalFormatting sqref="F2:F13">
+    <cfRule type="containsText" dxfId="57" priority="1" operator="containsText" text="pending">
+      <formula>NOT(ISERROR(SEARCH("pending",F2)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B8">
-    <cfRule type="containsText" dxfId="66" priority="10" operator="containsText" text="none">
-      <formula>NOT(ISERROR(SEARCH("none",B8)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B6">
-    <cfRule type="containsText" dxfId="65" priority="9" operator="containsText" text="none">
-      <formula>NOT(ISERROR(SEARCH("none",B6)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B7">
-    <cfRule type="containsText" dxfId="64" priority="8" operator="containsText" text="none">
-      <formula>NOT(ISERROR(SEARCH("none",B7)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B5">
-    <cfRule type="containsText" dxfId="63" priority="7" operator="containsText" text="none">
-      <formula>NOT(ISERROR(SEARCH("none",B5)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B4">
-    <cfRule type="containsText" dxfId="62" priority="6" operator="containsText" text="none">
-      <formula>NOT(ISERROR(SEARCH("none",B4)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B3">
-    <cfRule type="containsText" dxfId="61" priority="5" operator="containsText" text="none">
-      <formula>NOT(ISERROR(SEARCH("none",B2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F13">
-    <cfRule type="containsText" dxfId="60" priority="2" operator="containsText" text="done">
+    <cfRule type="containsText" dxfId="56" priority="2" operator="containsText" text="done">
       <formula>NOT(ISERROR(SEARCH("done",F2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F13">
-    <cfRule type="containsText" dxfId="59" priority="1" operator="containsText" text="pending">
-      <formula>NOT(ISERROR(SEARCH("pending",F2)))</formula>
+  <conditionalFormatting sqref="J2:J9">
+    <cfRule type="containsText" dxfId="55" priority="11" operator="containsText" text="none">
+      <formula>NOT(ISERROR(SEARCH("none",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8209,77 +8097,77 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A632C19-1341-4FE2-9EB2-326419CB9C3F}">
   <dimension ref="A1:M11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="44.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.140625" customWidth="1"/>
-    <col min="7" max="7" width="15.28515625" customWidth="1"/>
-    <col min="8" max="8" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="44.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.1640625" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" customWidth="1"/>
+    <col min="8" max="8" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="17" customFormat="1">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="G1" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="H1" s="17" t="s">
+      <c r="H1" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="I1" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="J1" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="K1" s="18" t="s">
+      <c r="K1" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="L1" s="17" t="s">
+      <c r="L1" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="M1" s="18" t="s">
+      <c r="M1" s="15" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="16"/>
+      <c r="B2" s="13"/>
       <c r="C2" t="s">
         <v>81</v>
       </c>
       <c r="D2" t="s">
         <v>186</v>
       </c>
-      <c r="E2" s="21"/>
-      <c r="F2" s="10" t="s">
+      <c r="E2" s="18"/>
+      <c r="F2" s="1" t="s">
         <v>80</v>
       </c>
       <c r="G2" t="s">
@@ -8292,7 +8180,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>83</v>
       </c>
@@ -8305,7 +8193,7 @@
       <c r="D3" t="s">
         <v>188</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="3">
         <v>1</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -8318,7 +8206,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>85</v>
       </c>
@@ -8331,7 +8219,7 @@
       <c r="D4" t="s">
         <v>189</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="3">
         <v>2</v>
       </c>
       <c r="F4" s="1" t="s">
@@ -8341,7 +8229,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>89</v>
       </c>
@@ -8354,7 +8242,7 @@
       <c r="D5" t="s">
         <v>190</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="3">
         <v>3</v>
       </c>
       <c r="F5" s="1" t="s">
@@ -8364,7 +8252,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>132</v>
       </c>
@@ -8377,7 +8265,7 @@
       <c r="D6" t="s">
         <v>191</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="3">
         <v>4</v>
       </c>
       <c r="F6" s="1" t="s">
@@ -8387,7 +8275,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>92</v>
       </c>
@@ -8400,14 +8288,14 @@
       <c r="D7" t="s">
         <v>192</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="3">
         <v>5</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>130</v>
       </c>
@@ -8420,14 +8308,14 @@
       <c r="D8" t="s">
         <v>193</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="3">
         <v>6</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>95</v>
       </c>
@@ -8440,14 +8328,14 @@
       <c r="D9" t="s">
         <v>194</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="3">
         <v>7</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>150</v>
       </c>
@@ -8460,7 +8348,7 @@
       <c r="D10" t="s">
         <v>195</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="3">
         <v>8</v>
       </c>
       <c r="F10" s="1" t="s">
@@ -8476,7 +8364,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>102</v>
       </c>
@@ -8489,7 +8377,7 @@
       <c r="D11" t="s">
         <v>196</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="4" t="s">
         <v>47</v>
       </c>
       <c r="F11" s="1" t="s">
@@ -8503,89 +8391,27 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B2:B11">
+    <cfRule type="containsText" dxfId="54" priority="7" operator="containsText" text="none">
+      <formula>NOT(ISERROR(SEARCH("none",B2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E11">
-    <cfRule type="containsText" dxfId="58" priority="18" operator="containsText" text="pending">
+    <cfRule type="containsText" dxfId="53" priority="18" operator="containsText" text="pending">
       <formula>NOT(ISERROR(SEARCH("pending",E11)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2">
-    <cfRule type="containsText" dxfId="57" priority="16" operator="containsText" text="none">
-      <formula>NOT(ISERROR(SEARCH("none",B2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B11">
-    <cfRule type="containsText" dxfId="56" priority="15" operator="containsText" text="none">
-      <formula>NOT(ISERROR(SEARCH("none",B11)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B3">
-    <cfRule type="containsText" dxfId="55" priority="14" operator="containsText" text="none">
-      <formula>NOT(ISERROR(SEARCH("none",B3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B5">
-    <cfRule type="containsText" dxfId="54" priority="13" operator="containsText" text="none">
-      <formula>NOT(ISERROR(SEARCH("none",B5)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B4">
-    <cfRule type="containsText" dxfId="53" priority="12" operator="containsText" text="none">
-      <formula>NOT(ISERROR(SEARCH("none",B4)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B6">
-    <cfRule type="containsText" dxfId="52" priority="11" operator="containsText" text="none">
-      <formula>NOT(ISERROR(SEARCH("none",B6)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B8">
-    <cfRule type="containsText" dxfId="51" priority="10" operator="containsText" text="none">
-      <formula>NOT(ISERROR(SEARCH("none",B8)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B7">
-    <cfRule type="containsText" dxfId="50" priority="9" operator="containsText" text="none">
-      <formula>NOT(ISERROR(SEARCH("none",B7)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B9">
-    <cfRule type="containsText" dxfId="49" priority="8" operator="containsText" text="none">
-      <formula>NOT(ISERROR(SEARCH("none",B9)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B10">
-    <cfRule type="containsText" dxfId="48" priority="7" operator="containsText" text="none">
-      <formula>NOT(ISERROR(SEARCH("none",B10)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F3:F10">
-    <cfRule type="containsText" dxfId="47" priority="6" operator="containsText" text="done">
-      <formula>NOT(ISERROR(SEARCH("done",F3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F3:F10">
-    <cfRule type="containsText" dxfId="46" priority="5" operator="containsText" text="pending">
-      <formula>NOT(ISERROR(SEARCH("pending",F3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F11">
-    <cfRule type="containsText" dxfId="45" priority="4" operator="containsText" text="done">
-      <formula>NOT(ISERROR(SEARCH("done",F11)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F11">
-    <cfRule type="containsText" dxfId="44" priority="3" operator="containsText" text="pending">
-      <formula>NOT(ISERROR(SEARCH("pending",F11)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E2">
-    <cfRule type="cellIs" dxfId="43" priority="2" operator="equal">
+  <conditionalFormatting sqref="E2:F2">
+    <cfRule type="cellIs" dxfId="52" priority="1" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2">
-    <cfRule type="cellIs" dxfId="42" priority="1" operator="equal">
-      <formula>"N/A"</formula>
+  <conditionalFormatting sqref="F3:F11">
+    <cfRule type="containsText" dxfId="51" priority="3" operator="containsText" text="pending">
+      <formula>NOT(ISERROR(SEARCH("pending",F3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="50" priority="4" operator="containsText" text="done">
+      <formula>NOT(ISERROR(SEARCH("done",F3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8595,69 +8421,69 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F20394B1-9E8C-44C9-867A-4645390B3BCA}">
   <dimension ref="A1:N17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.85546875" customWidth="1"/>
-    <col min="3" max="3" width="42.5703125" customWidth="1"/>
-    <col min="4" max="4" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="42.5" customWidth="1"/>
+    <col min="4" max="4" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="17" customFormat="1">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:14" s="14" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="G1" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="H1" s="17" t="s">
+      <c r="H1" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="I1" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="J1" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="K1" s="18" t="s">
+      <c r="K1" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="L1" s="17" t="s">
+      <c r="L1" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="M1" s="17" t="s">
+      <c r="M1" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="N1" s="18" t="s">
+      <c r="N1" s="15" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>75</v>
       </c>
@@ -8667,14 +8493,14 @@
       <c r="C2" t="s">
         <v>201</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="3">
         <v>1</v>
       </c>
-      <c r="E2" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
+      <c r="E2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
       <c r="H2" t="s">
         <v>80</v>
       </c>
@@ -8697,7 +8523,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>83</v>
       </c>
@@ -8707,7 +8533,7 @@
       <c r="C3" t="s">
         <v>206</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="3">
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -8737,7 +8563,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>84</v>
       </c>
@@ -8747,7 +8573,7 @@
       <c r="C4" t="s">
         <v>210</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="3">
         <v>3</v>
       </c>
       <c r="E4" s="1" t="s">
@@ -8777,7 +8603,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>85</v>
       </c>
@@ -8787,7 +8613,7 @@
       <c r="C5" t="s">
         <v>215</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="3">
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
@@ -8814,7 +8640,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>89</v>
       </c>
@@ -8824,7 +8650,7 @@
       <c r="C6" t="s">
         <v>222</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="3">
         <v>5</v>
       </c>
       <c r="E6" s="1" t="s">
@@ -8844,7 +8670,7 @@
       <c r="K6" t="s">
         <v>203</v>
       </c>
-      <c r="L6" s="11" t="s">
+      <c r="L6" s="8" t="s">
         <v>226</v>
       </c>
       <c r="M6" t="s">
@@ -8854,7 +8680,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>145</v>
       </c>
@@ -8864,7 +8690,7 @@
       <c r="C7" t="s">
         <v>230</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="3">
         <v>6</v>
       </c>
       <c r="E7" s="1" t="s">
@@ -8894,7 +8720,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>95</v>
       </c>
@@ -8904,7 +8730,7 @@
       <c r="C8" t="s">
         <v>236</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="3">
         <v>7</v>
       </c>
       <c r="E8" s="1" t="s">
@@ -8934,7 +8760,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>146</v>
       </c>
@@ -8944,7 +8770,7 @@
       <c r="C9" t="s">
         <v>241</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="3">
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
@@ -8974,7 +8800,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>147</v>
       </c>
@@ -8984,7 +8810,7 @@
       <c r="C10" t="s">
         <v>247</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="3">
         <v>9</v>
       </c>
       <c r="E10" s="1" t="s">
@@ -9014,14 +8840,14 @@
         <v>80</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>250</v>
       </c>
       <c r="C11" t="s">
         <v>251</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="3">
         <v>10</v>
       </c>
       <c r="E11" s="1" t="s">
@@ -9051,14 +8877,14 @@
         <v>80</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>255</v>
       </c>
       <c r="C12" t="s">
         <v>256</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="3">
         <v>11</v>
       </c>
       <c r="E12" s="1" t="s">
@@ -9088,7 +8914,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>150</v>
       </c>
@@ -9098,7 +8924,7 @@
       <c r="C13" t="s">
         <v>260</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="3">
         <v>12</v>
       </c>
       <c r="E13" s="1" t="s">
@@ -9122,7 +8948,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>102</v>
       </c>
@@ -9132,7 +8958,7 @@
       <c r="C14" t="s">
         <v>201</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="4" t="s">
         <v>47</v>
       </c>
       <c r="E14" s="1" t="s">
@@ -9147,53 +8973,36 @@
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="2:2">
-      <c r="B17" s="19"/>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B17" s="16"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E3:G13">
-    <cfRule type="containsText" dxfId="41" priority="9" operator="containsText" text="done">
-      <formula>NOT(ISERROR(SEARCH("done",E3)))</formula>
+  <conditionalFormatting sqref="A1:XFD6 A7:K7 M7:XFD7 A8 C8:XFD8 A9:XFD1048576">
+    <cfRule type="cellIs" dxfId="49" priority="1" operator="equal">
+      <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E3:G13">
-    <cfRule type="containsText" dxfId="40" priority="8" operator="containsText" text="pending">
-      <formula>NOT(ISERROR(SEARCH("pending",E3)))</formula>
+  <conditionalFormatting sqref="B2:B7">
+    <cfRule type="containsText" dxfId="48" priority="6" operator="containsText" text="none">
+      <formula>NOT(ISERROR(SEARCH("none",B2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B9:B14">
+    <cfRule type="containsText" dxfId="47" priority="4" operator="containsText" text="none">
+      <formula>NOT(ISERROR(SEARCH("none",B9)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="containsText" dxfId="39" priority="7" operator="containsText" text="pending">
+    <cfRule type="containsText" dxfId="46" priority="7" operator="containsText" text="pending">
       <formula>NOT(ISERROR(SEARCH("pending",D14)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B7 B9:B12">
-    <cfRule type="containsText" dxfId="38" priority="6" operator="containsText" text="none">
-      <formula>NOT(ISERROR(SEARCH("none",B2)))</formula>
+  <conditionalFormatting sqref="E3:G14">
+    <cfRule type="containsText" dxfId="45" priority="2" operator="containsText" text="pending">
+      <formula>NOT(ISERROR(SEARCH("pending",E3)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B14">
-    <cfRule type="containsText" dxfId="37" priority="5" operator="containsText" text="none">
-      <formula>NOT(ISERROR(SEARCH("none",B14)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B13">
-    <cfRule type="containsText" dxfId="36" priority="4" operator="containsText" text="none">
-      <formula>NOT(ISERROR(SEARCH("none",B13)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E14:G14">
-    <cfRule type="containsText" dxfId="35" priority="3" operator="containsText" text="done">
-      <formula>NOT(ISERROR(SEARCH("done",E14)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E14:G14">
-    <cfRule type="containsText" dxfId="34" priority="2" operator="containsText" text="pending">
-      <formula>NOT(ISERROR(SEARCH("pending",E14)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A8 A1:XFD6 A7:K7 M7:XFD7 C8:XFD8 A9:XFD1048576">
-    <cfRule type="cellIs" dxfId="33" priority="1" operator="equal">
-      <formula>"N/A"</formula>
+    <cfRule type="containsText" dxfId="44" priority="3" operator="containsText" text="done">
+      <formula>NOT(ISERROR(SEARCH("done",E3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
